--- a/diseases/d017/2026-2029.xlsx
+++ b/diseases/d017/2026-2029.xlsx
@@ -24206,6 +24206,154 @@
         </is>
       </c>
     </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>D017</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>measles</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>D017</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>麻疹</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N138" t="n">
+        <v>1</v>
+      </c>
+      <c r="O138" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S138" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO138" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP138" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR138" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS138" t="inlineStr"/>
+      <c r="AT138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU138" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV138" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW138" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX138" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY138" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA138" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB138" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC138" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -24239,7 +24387,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
     </row>
@@ -24322,7 +24470,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="10">
@@ -24332,7 +24480,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="11">
@@ -24384,7 +24532,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1287</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d017/2026-2029.xlsx
+++ b/diseases/d017/2026-2029.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>1</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="S3" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1306,9 +1303,6 @@
       <c r="O5" t="n">
         <v>2</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>0.02220298456959181</v>
       </c>
@@ -1602,9 +1596,6 @@
       <c r="O7" t="n">
         <v>0</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
         <v>0</v>
       </c>
@@ -1998,9 +1989,6 @@
       <c r="O9" t="n">
         <v>0</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
@@ -2146,9 +2134,6 @@
       <c r="O10" t="n">
         <v>0</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0</v>
       </c>
@@ -2294,9 +2279,6 @@
       <c r="O11" t="n">
         <v>0</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
       <c r="R11" t="n">
         <v>0</v>
       </c>
@@ -2939,7 +2921,7 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN14" t="b">
@@ -3086,9 +3068,6 @@
       <c r="O15" t="n">
         <v>2</v>
       </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
       <c r="R15" t="n">
         <v>0.01868976085656669</v>
       </c>
@@ -4222,9 +4201,6 @@
       <c r="O22" t="n">
         <v>5</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="S22" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -4615,9 +4591,6 @@
       <c r="O24" t="n">
         <v>0</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>0</v>
       </c>
@@ -4911,9 +4884,6 @@
       <c r="O26" t="n">
         <v>0</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>0</v>
       </c>
@@ -5307,9 +5277,6 @@
       <c r="O28" t="n">
         <v>0</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>0</v>
       </c>
@@ -5455,9 +5422,6 @@
       <c r="O29" t="n">
         <v>3</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>0.005813909771376137</v>
       </c>
@@ -5603,9 +5567,6 @@
       <c r="O30" t="n">
         <v>0</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0</v>
       </c>
@@ -6248,7 +6209,7 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN33" t="b">
@@ -6395,9 +6356,6 @@
       <c r="O34" t="n">
         <v>1</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>0.009344880428283346</v>
       </c>
@@ -7679,9 +7637,6 @@
       <c r="O42" t="n">
         <v>15</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="S42" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -8072,9 +8027,6 @@
       <c r="O44" t="n">
         <v>2</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>0.02220298456959181</v>
       </c>
@@ -8368,9 +8320,6 @@
       <c r="O46" t="n">
         <v>0</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>0</v>
       </c>
@@ -8764,9 +8713,6 @@
       <c r="O48" t="n">
         <v>1</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>0.01355270280196709</v>
       </c>
@@ -8912,9 +8858,6 @@
       <c r="O49" t="n">
         <v>1</v>
       </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
       <c r="R49" t="n">
         <v>0.001937969923792046</v>
       </c>
@@ -9060,9 +9003,6 @@
       <c r="O50" t="n">
         <v>0</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0</v>
       </c>
@@ -9705,7 +9645,7 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN53" t="b">
@@ -9852,9 +9792,6 @@
       <c r="O54" t="n">
         <v>1</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>0.009344880428283346</v>
       </c>
@@ -10988,9 +10925,6 @@
       <c r="O61" t="n">
         <v>6</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>0.02203687091711874</v>
       </c>
@@ -11136,9 +11070,6 @@
       <c r="O62" t="n">
         <v>3</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="S62" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -11529,9 +11460,6 @@
       <c r="O64" t="n">
         <v>7</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>0.07771044599357135</v>
       </c>
@@ -11825,9 +11753,6 @@
       <c r="O66" t="n">
         <v>0</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
         <v>0</v>
       </c>
@@ -12221,9 +12146,6 @@
       <c r="O68" t="n">
         <v>6</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>0.08131621681180255</v>
       </c>
@@ -12369,9 +12291,6 @@
       <c r="O69" t="n">
         <v>2</v>
       </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
       <c r="R69" t="n">
         <v>0.003875939847584092</v>
       </c>
@@ -12517,9 +12436,6 @@
       <c r="O70" t="n">
         <v>0</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>0</v>
       </c>
@@ -12913,9 +12829,6 @@
       <c r="O72" t="n">
         <v>2</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0.03782520932943658</v>
       </c>
@@ -13162,7 +13075,7 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN73" t="b">
@@ -13309,9 +13222,6 @@
       <c r="O74" t="n">
         <v>1</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>0.009344880428283346</v>
       </c>
@@ -13705,9 +13615,6 @@
       <c r="O76" t="n">
         <v>5</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="R76" t="n">
         <v>0.02172846223218448</v>
       </c>
@@ -14445,9 +14352,6 @@
       <c r="O81" t="n">
         <v>0</v>
       </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
       <c r="R81" t="n">
         <v>0</v>
       </c>
@@ -14593,9 +14497,6 @@
       <c r="O82" t="n">
         <v>3</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="S82" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -14986,9 +14887,6 @@
       <c r="O84" t="n">
         <v>5</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>0.05550746142397953</v>
       </c>
@@ -15282,9 +15180,6 @@
       <c r="O86" t="n">
         <v>0</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0</v>
       </c>
@@ -15678,9 +15573,6 @@
       <c r="O88" t="n">
         <v>0</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>0</v>
       </c>
@@ -15826,9 +15718,6 @@
       <c r="O89" t="n">
         <v>1</v>
       </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
       <c r="R89" t="n">
         <v>0.001937969923792046</v>
       </c>
@@ -15974,9 +15863,6 @@
       <c r="O90" t="n">
         <v>1</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>0.01768975825795506</v>
       </c>
@@ -16370,9 +16256,6 @@
       <c r="O92" t="n">
         <v>2</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>0.03782520932943658</v>
       </c>
@@ -16619,7 +16502,7 @@
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN93" t="b">
@@ -16766,9 +16649,6 @@
       <c r="O94" t="n">
         <v>0</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>0</v>
       </c>
@@ -17162,9 +17042,6 @@
       <c r="O96" t="n">
         <v>2</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="R96" t="n">
         <v>0.008691384892873792</v>
       </c>
@@ -18050,9 +17927,6 @@
       <c r="O102" t="n">
         <v>0</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>0</v>
       </c>
@@ -18198,9 +18072,6 @@
       <c r="O103" t="n">
         <v>1</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="R103" t="n">
         <v>0.01110149228479591</v>
       </c>
@@ -18494,9 +18365,6 @@
       <c r="O105" t="n">
         <v>0</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="R105" t="n">
         <v>0</v>
       </c>
@@ -18890,9 +18758,6 @@
       <c r="O107" t="n">
         <v>1</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>0.01355270280196709</v>
       </c>
@@ -19038,9 +18903,6 @@
       <c r="O108" t="n">
         <v>1</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="R108" t="n">
         <v>0.001937969923792046</v>
       </c>
@@ -19186,9 +19048,6 @@
       <c r="O109" t="n">
         <v>0</v>
       </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
       <c r="R109" t="n">
         <v>0</v>
       </c>
@@ -19582,9 +19441,6 @@
       <c r="O111" t="n">
         <v>0</v>
       </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
       <c r="R111" t="n">
         <v>0</v>
       </c>
@@ -19831,7 +19687,7 @@
       </c>
       <c r="AM112" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN112" t="b">
@@ -19978,9 +19834,6 @@
       <c r="O113" t="n">
         <v>0</v>
       </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
       <c r="R113" t="n">
         <v>0</v>
       </c>
@@ -20374,9 +20227,6 @@
       <c r="O115" t="n">
         <v>11</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>0.00898489248322343</v>
       </c>
@@ -20522,9 +20372,6 @@
       <c r="O116" t="n">
         <v>2</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="R116" t="n">
         <v>0.001633616815131532</v>
       </c>
@@ -20670,9 +20517,6 @@
       <c r="O117" t="n">
         <v>5</v>
       </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
       <c r="R117" t="n">
         <v>0.004084042037828832</v>
       </c>
@@ -20818,9 +20662,6 @@
       <c r="O118" t="n">
         <v>8</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="R118" t="n">
         <v>0.00653446726052613</v>
       </c>
@@ -20966,9 +20807,6 @@
       <c r="O119" t="n">
         <v>0</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
         <v>0</v>
       </c>
@@ -21114,9 +20952,6 @@
       <c r="O120" t="n">
         <v>0</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>0</v>
       </c>
@@ -21510,9 +21345,6 @@
       <c r="O122" t="n">
         <v>2</v>
       </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
       <c r="R122" t="n">
         <v>0.003875939847584092</v>
       </c>
@@ -21658,9 +21490,6 @@
       <c r="O123" t="n">
         <v>0</v>
       </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
       <c r="R123" t="n">
         <v>0</v>
       </c>
@@ -22054,9 +21883,6 @@
       <c r="O125" t="n">
         <v>0</v>
       </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
       <c r="R125" t="n">
         <v>0</v>
       </c>
@@ -22450,9 +22276,6 @@
       <c r="O127" t="n">
         <v>6</v>
       </c>
-      <c r="Q127" t="n">
-        <v>0</v>
-      </c>
       <c r="R127" t="n">
         <v>0.004900850445394598</v>
       </c>
@@ -22598,9 +22421,6 @@
       <c r="O128" t="n">
         <v>3</v>
       </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
       <c r="R128" t="n">
         <v>0.002450425222697299</v>
       </c>
@@ -22746,9 +22566,6 @@
       <c r="O129" t="n">
         <v>0</v>
       </c>
-      <c r="Q129" t="n">
-        <v>0</v>
-      </c>
       <c r="R129" t="n">
         <v>0</v>
       </c>
@@ -22894,9 +22711,6 @@
       <c r="O130" t="n">
         <v>1</v>
       </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
       <c r="R130" t="n">
         <v>0.0008168084075657662</v>
       </c>
@@ -23042,9 +22856,6 @@
       <c r="O131" t="n">
         <v>0</v>
       </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
       <c r="R131" t="n">
         <v>0</v>
       </c>
@@ -23190,9 +23001,6 @@
       <c r="O132" t="n">
         <v>0</v>
       </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
       <c r="R132" t="n">
         <v>0</v>
       </c>
@@ -23338,9 +23146,6 @@
       <c r="O133" t="n">
         <v>0</v>
       </c>
-      <c r="Q133" t="n">
-        <v>0</v>
-      </c>
       <c r="R133" t="n">
         <v>0</v>
       </c>
@@ -23734,9 +23539,6 @@
       <c r="O135" t="n">
         <v>0</v>
       </c>
-      <c r="Q135" t="n">
-        <v>0</v>
-      </c>
       <c r="R135" t="n">
         <v>0</v>
       </c>
@@ -23882,9 +23684,6 @@
       <c r="O136" t="n">
         <v>0</v>
       </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
       <c r="R136" t="n">
         <v>0</v>
       </c>
@@ -24277,9 +24076,6 @@
       </c>
       <c r="O138" t="n">
         <v>1</v>
-      </c>
-      <c r="Q138" t="n">
-        <v>0</v>
       </c>
       <c r="R138" t="n">
         <v>0.0008168084075657662</v>

--- a/diseases/d017/2026-2029.xlsx
+++ b/diseases/d017/2026-2029.xlsx
@@ -18028,12 +18028,12 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -18067,81 +18067,92 @@
         </is>
       </c>
       <c r="N103" t="n">
+        <v>2</v>
+      </c>
+      <c r="O103" t="n">
+        <v>2</v>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_MEASLES_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO103" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP103" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ103" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS103" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_MEASLES_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT103" t="n">
         <v>1</v>
       </c>
-      <c r="O103" t="n">
-        <v>1</v>
-      </c>
-      <c r="R103" t="n">
-        <v>0.01110149228479591</v>
-      </c>
-      <c r="S103" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO103" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP103" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR103" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS103" t="inlineStr"/>
-      <c r="AT103" t="n">
-        <v>0</v>
-      </c>
       <c r="AU103" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV103" t="inlineStr">
         <is>
-          <t>foph_idd</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Switzerland FOPH IDD</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
         <is>
-          <t>rest_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>foph_idd</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA103" t="inlineStr">
         <is>
-          <t>Switzerland FOPH IDD</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB103" t="inlineStr">
         <is>
-          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC103" t="inlineStr">
         <is>
-          <t>rest_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -18168,17 +18179,17 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -18212,84 +18223,170 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>76</v>
+        <v>2</v>
       </c>
       <c r="O104" t="n">
-        <v>76</v>
-      </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
-      <c r="R104" t="n">
-        <v>0.005378954079273447</v>
-      </c>
-      <c r="S104" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_MEASLES_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_MEASLES_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>SRC_CA_ON_PHO_IDTO</t>
+        </is>
+      </c>
+      <c r="X104" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>country:CA-ON:national</t>
+        </is>
+      </c>
+      <c r="AD104" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE104" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF104" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG104" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH104" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI104" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ104" t="inlineStr">
+        <is>
+          <t>PHO_IDTO_2026_07</t>
+        </is>
+      </c>
+      <c r="AK104" t="inlineStr">
+        <is>
+          <t>PHO IDTO current-year monthly preliminary measles notifications; confirmed cases only, with reportable probable cases excluded from the tool's temporal trend.</t>
+        </is>
+      </c>
+      <c r="AM104" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN104" t="b">
+        <v>1</v>
       </c>
       <c r="AO104" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR104" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS104" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ104" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS104" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_MEASLES_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU104" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV104" t="inlineStr">
         <is>
-          <t>cdc_weekly</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>China CDC Weekly</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>cdc_weekly; nhc; pubmed</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA104" t="inlineStr">
         <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB104" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC104" t="inlineStr">
         <is>
-          <t>web; web; web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -18321,12 +18418,12 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -18360,95 +18457,81 @@
         </is>
       </c>
       <c r="N105" t="n">
+        <v>1</v>
+      </c>
+      <c r="O105" t="n">
+        <v>1</v>
+      </c>
+      <c r="R105" t="n">
+        <v>0.01110149228479591</v>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO105" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP105" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR105" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS105" t="inlineStr"/>
+      <c r="AT105" t="n">
         <v>0</v>
       </c>
-      <c r="O105" t="n">
-        <v>0</v>
-      </c>
-      <c r="R105" t="n">
-        <v>0</v>
-      </c>
-      <c r="S105" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U105" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_170</t>
-        </is>
-      </c>
-      <c r="AA105" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO105" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP105" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ105" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS105" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_170</t>
-        </is>
-      </c>
-      <c r="AT105" t="n">
-        <v>1</v>
-      </c>
       <c r="AU105" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV105" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>rest_api</t>
         </is>
       </c>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="BA105" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="BB105" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="BC105" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>rest_api</t>
         </is>
       </c>
     </row>
@@ -18475,17 +18558,17 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -18519,170 +18602,84 @@
         </is>
       </c>
       <c r="N106" t="n">
+        <v>76</v>
+      </c>
+      <c r="O106" t="n">
+        <v>76</v>
+      </c>
+      <c r="Q106" t="n">
         <v>0</v>
       </c>
-      <c r="O106" t="n">
+      <c r="R106" t="n">
+        <v>0.005378954079273447</v>
+      </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO106" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP106" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR106" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS106" t="inlineStr"/>
+      <c r="AT106" t="n">
         <v>0</v>
       </c>
-      <c r="U106" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_170</t>
-        </is>
-      </c>
-      <c r="V106" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_170</t>
-        </is>
-      </c>
-      <c r="W106" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X106" t="inlineStr">
-        <is>
-          <t>Cinderella disease</t>
-        </is>
-      </c>
-      <c r="Y106" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z106" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA106" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB106" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD106" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE106" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF106" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG106" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH106" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI106" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ106" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK106" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; The English cube mistranslates Finnish Tuhkarokko; source code 170 is measles.</t>
-        </is>
-      </c>
-      <c r="AM106" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN106" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO106" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP106" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ106" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS106" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_170</t>
-        </is>
-      </c>
-      <c r="AT106" t="n">
-        <v>1</v>
-      </c>
       <c r="AU106" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV106" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA106" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB106" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC106" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -18714,12 +18711,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -18753,81 +18750,95 @@
         </is>
       </c>
       <c r="N107" t="n">
+        <v>0</v>
+      </c>
+      <c r="O107" t="n">
+        <v>0</v>
+      </c>
+      <c r="R107" t="n">
+        <v>0</v>
+      </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_170</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO107" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP107" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ107" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS107" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_170</t>
+        </is>
+      </c>
+      <c r="AT107" t="n">
         <v>1</v>
       </c>
-      <c r="O107" t="n">
-        <v>1</v>
-      </c>
-      <c r="R107" t="n">
-        <v>0.01355270280196709</v>
-      </c>
-      <c r="S107" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO107" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP107" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR107" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS107" t="inlineStr"/>
-      <c r="AT107" t="n">
-        <v>0</v>
-      </c>
       <c r="AU107" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV107" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA107" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB107" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC107" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -18854,17 +18865,17 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -18898,81 +18909,170 @@
         </is>
       </c>
       <c r="N108" t="n">
+        <v>0</v>
+      </c>
+      <c r="O108" t="n">
+        <v>0</v>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_170</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_170</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X108" t="inlineStr">
+        <is>
+          <t>Cinderella disease</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD108" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE108" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF108" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG108" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH108" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI108" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ108" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK108" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; The English cube mistranslates Finnish Tuhkarokko; source code 170 is measles.</t>
+        </is>
+      </c>
+      <c r="AM108" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN108" t="b">
         <v>1</v>
       </c>
-      <c r="O108" t="n">
+      <c r="AO108" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP108" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ108" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS108" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_170</t>
+        </is>
+      </c>
+      <c r="AT108" t="n">
         <v>1</v>
       </c>
-      <c r="R108" t="n">
-        <v>0.001937969923792046</v>
-      </c>
-      <c r="S108" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO108" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP108" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR108" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS108" t="inlineStr"/>
-      <c r="AT108" t="n">
-        <v>0</v>
-      </c>
       <c r="AU108" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV108" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA108" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB108" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC108" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -19004,12 +19104,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -19043,95 +19143,81 @@
         </is>
       </c>
       <c r="N109" t="n">
+        <v>1</v>
+      </c>
+      <c r="O109" t="n">
+        <v>1</v>
+      </c>
+      <c r="R109" t="n">
+        <v>0.01355270280196709</v>
+      </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO109" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP109" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR109" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS109" t="inlineStr"/>
+      <c r="AT109" t="n">
         <v>0</v>
       </c>
-      <c r="O109" t="n">
-        <v>0</v>
-      </c>
-      <c r="R109" t="n">
-        <v>0</v>
-      </c>
-      <c r="S109" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U109" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA109" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO109" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP109" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ109" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS109" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AT109" t="n">
-        <v>1</v>
-      </c>
       <c r="AU109" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV109" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA109" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB109" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC109" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -19158,17 +19244,17 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -19202,170 +19288,81 @@
         </is>
       </c>
       <c r="N110" t="n">
+        <v>1</v>
+      </c>
+      <c r="O110" t="n">
+        <v>1</v>
+      </c>
+      <c r="R110" t="n">
+        <v>0.001937969923792046</v>
+      </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO110" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP110" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR110" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS110" t="inlineStr"/>
+      <c r="AT110" t="n">
         <v>0</v>
       </c>
-      <c r="O110" t="n">
-        <v>0</v>
-      </c>
-      <c r="U110" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V110" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W110" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X110" t="inlineStr">
-        <is>
-          <t>Meslinger</t>
-        </is>
-      </c>
-      <c r="Y110" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z110" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA110" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB110" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD110" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE110" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF110" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG110" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH110" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI110" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ110" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK110" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM110" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN110" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO110" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP110" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ110" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS110" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AT110" t="n">
-        <v>1</v>
-      </c>
       <c r="AU110" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV110" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA110" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB110" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC110" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -19397,12 +19394,12 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -19451,7 +19448,7 @@
       </c>
       <c r="U111" t="inlineStr">
         <is>
-          <t>SER_NZ_MEASLES_MONTHLY</t>
+          <t>SER_NO_FHI_107_MONTHLY</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -19476,7 +19473,7 @@
       </c>
       <c r="AS111" t="inlineStr">
         <is>
-          <t>SER_NZ_MEASLES_MONTHLY</t>
+          <t>SER_NO_FHI_107_MONTHLY</t>
         </is>
       </c>
       <c r="AT111" t="n">
@@ -19489,42 +19486,42 @@
       </c>
       <c r="AV111" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA111" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB111" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC111" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -19556,12 +19553,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -19602,22 +19599,22 @@
       </c>
       <c r="U112" t="inlineStr">
         <is>
-          <t>SER_NZ_MEASLES_MONTHLY</t>
+          <t>SER_NO_FHI_107_MONTHLY</t>
         </is>
       </c>
       <c r="V112" t="inlineStr">
         <is>
-          <t>SER_NZ_MEASLES_MONTHLY</t>
+          <t>SER_NO_FHI_107_MONTHLY</t>
         </is>
       </c>
       <c r="W112" t="inlineStr">
         <is>
-          <t>SRC_NZ_PHS</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X112" t="inlineStr">
         <is>
-          <t>Measles</t>
+          <t>Meslinger</t>
         </is>
       </c>
       <c r="Y112" t="inlineStr">
@@ -19627,7 +19624,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -19642,7 +19639,7 @@
       </c>
       <c r="AC112" t="inlineStr">
         <is>
-          <t>country:NZ:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD112" t="inlineStr">
@@ -19677,17 +19674,17 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>NZ_PHS_current</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK112" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science monthly measles notifications.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
       <c r="AM112" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN112" t="b">
@@ -19710,7 +19707,7 @@
       </c>
       <c r="AS112" t="inlineStr">
         <is>
-          <t>SER_NZ_MEASLES_MONTHLY</t>
+          <t>SER_NO_FHI_107_MONTHLY</t>
         </is>
       </c>
       <c r="AT112" t="n">
@@ -19723,42 +19720,42 @@
       </c>
       <c r="AV112" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA112" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB112" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC112" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -19790,12 +19787,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -19844,7 +19841,7 @@
       </c>
       <c r="U113" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_MEASLES</t>
+          <t>SER_NZ_MEASLES_MONTHLY</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -19869,7 +19866,7 @@
       </c>
       <c r="AS113" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_MEASLES</t>
+          <t>SER_NZ_MEASLES_MONTHLY</t>
         </is>
       </c>
       <c r="AT113" t="n">
@@ -19882,42 +19879,42 @@
       </c>
       <c r="AV113" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA113" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB113" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC113" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -19949,12 +19946,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -19995,22 +19992,22 @@
       </c>
       <c r="U114" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_MEASLES</t>
+          <t>SER_NZ_MEASLES_MONTHLY</t>
         </is>
       </c>
       <c r="V114" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_MEASLES</t>
+          <t>SER_NZ_MEASLES_MONTHLY</t>
         </is>
       </c>
       <c r="W114" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NZ_PHS</t>
         </is>
       </c>
       <c r="X114" t="inlineStr">
         <is>
-          <t>Mässling</t>
+          <t>Measles</t>
         </is>
       </c>
       <c r="Y114" t="inlineStr">
@@ -20020,7 +20017,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -20035,7 +20032,7 @@
       </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NZ:national</t>
         </is>
       </c>
       <c r="AD114" t="inlineStr">
@@ -20070,17 +20067,17 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NZ_PHS_current</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+          <t>New Zealand PHF Science monthly measles notifications.</t>
         </is>
       </c>
       <c r="AM114" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN114" t="b">
@@ -20103,7 +20100,7 @@
       </c>
       <c r="AS114" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_MEASLES</t>
+          <t>SER_NZ_MEASLES_MONTHLY</t>
         </is>
       </c>
       <c r="AT114" t="n">
@@ -20116,42 +20113,42 @@
       </c>
       <c r="AV114" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA114" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB114" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC114" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -20183,12 +20180,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -20213,7 +20210,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
@@ -20222,81 +20219,95 @@
         </is>
       </c>
       <c r="N115" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O115" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="R115" t="n">
-        <v>0.00898489248322343</v>
+        <v>0</v>
       </c>
       <c r="S115" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MEASLES</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO115" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP115" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR115" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS115" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ115" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS115" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MEASLES</t>
+        </is>
+      </c>
       <c r="AT115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU115" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV115" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA115" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB115" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC115" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -20323,17 +20334,17 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -20358,7 +20369,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
@@ -20367,81 +20378,170 @@
         </is>
       </c>
       <c r="N116" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O116" t="n">
-        <v>2</v>
-      </c>
-      <c r="R116" t="n">
-        <v>0.001633616815131532</v>
-      </c>
-      <c r="S116" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MEASLES</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MEASLES</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X116" t="inlineStr">
+        <is>
+          <t>Mässling</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD116" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE116" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF116" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG116" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH116" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI116" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ116" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK116" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM116" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN116" t="b">
+        <v>1</v>
       </c>
       <c r="AO116" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP116" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR116" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS116" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ116" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS116" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MEASLES</t>
+        </is>
+      </c>
       <c r="AT116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU116" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV116" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA116" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB116" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC116" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -20503,7 +20603,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
@@ -20512,13 +20612,13 @@
         </is>
       </c>
       <c r="N117" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="O117" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="R117" t="n">
-        <v>0.004084042037828832</v>
+        <v>0.00898489248322343</v>
       </c>
       <c r="S117" t="inlineStr">
         <is>
@@ -20648,7 +20748,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
@@ -20657,13 +20757,13 @@
         </is>
       </c>
       <c r="N118" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="O118" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="R118" t="n">
-        <v>0.00653446726052613</v>
+        <v>0.001633616815131532</v>
       </c>
       <c r="S118" t="inlineStr">
         <is>
@@ -20763,12 +20863,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -20793,22 +20893,22 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N119" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O119" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R119" t="n">
-        <v>0</v>
+        <v>0.004084042037828832</v>
       </c>
       <c r="S119" t="inlineStr">
         <is>
@@ -20841,42 +20941,42 @@
       </c>
       <c r="AV119" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA119" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB119" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC119" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -20908,12 +21008,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -20938,104 +21038,90 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N120" t="n">
+        <v>8</v>
+      </c>
+      <c r="O120" t="n">
+        <v>8</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.00653446726052613</v>
+      </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO120" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP120" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR120" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS120" t="inlineStr"/>
+      <c r="AT120" t="n">
         <v>0</v>
       </c>
-      <c r="O120" t="n">
-        <v>0</v>
-      </c>
-      <c r="R120" t="n">
-        <v>0</v>
-      </c>
-      <c r="S120" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U120" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_170</t>
-        </is>
-      </c>
-      <c r="AA120" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO120" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP120" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ120" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS120" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_170</t>
-        </is>
-      </c>
-      <c r="AT120" t="n">
-        <v>1</v>
-      </c>
       <c r="AU120" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV120" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA120" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB120" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC120" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -21062,17 +21148,17 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -21111,165 +21197,76 @@
       <c r="O121" t="n">
         <v>0</v>
       </c>
-      <c r="U121" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_170</t>
-        </is>
-      </c>
-      <c r="V121" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_170</t>
-        </is>
-      </c>
-      <c r="W121" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X121" t="inlineStr">
-        <is>
-          <t>Cinderella disease</t>
-        </is>
-      </c>
-      <c r="Y121" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z121" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA121" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB121" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD121" t="inlineStr">
+      <c r="R121" t="n">
+        <v>0</v>
+      </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO121" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP121" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR121" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS121" t="inlineStr"/>
+      <c r="AT121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU121" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV121" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE121" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF121" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG121" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH121" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI121" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ121" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK121" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; The English cube mistranslates Finnish Tuhkarokko; source code 170 is measles.</t>
-        </is>
-      </c>
-      <c r="AM121" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN121" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO121" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP121" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ121" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS121" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_170</t>
-        </is>
-      </c>
-      <c r="AT121" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU121" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV121" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA121" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB121" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC121" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -21301,12 +21298,12 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -21340,81 +21337,95 @@
         </is>
       </c>
       <c r="N122" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O122" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R122" t="n">
-        <v>0.003875939847584092</v>
+        <v>0</v>
       </c>
       <c r="S122" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_170</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO122" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP122" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR122" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS122" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ122" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS122" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_170</t>
+        </is>
+      </c>
       <c r="AT122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU122" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV122" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA122" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB122" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC122" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -21441,17 +21452,17 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -21490,17 +21501,34 @@
       <c r="O123" t="n">
         <v>0</v>
       </c>
-      <c r="R123" t="n">
-        <v>0</v>
-      </c>
-      <c r="S123" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U123" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
+          <t>SER_FI_THL_TTR_170</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_170</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X123" t="inlineStr">
+        <is>
+          <t>Cinderella disease</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -21508,6 +21536,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD123" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE123" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF123" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG123" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH123" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI123" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ123" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK123" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; The English cube mistranslates Finnish Tuhkarokko; source code 170 is measles.</t>
+        </is>
+      </c>
+      <c r="AM123" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN123" t="b">
+        <v>1</v>
+      </c>
       <c r="AO123" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -21520,12 +21606,12 @@
       </c>
       <c r="AQ123" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS123" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
+          <t>SER_FI_THL_TTR_170</t>
         </is>
       </c>
       <c r="AT123" t="n">
@@ -21533,47 +21619,47 @@
       </c>
       <c r="AU123" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV123" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA123" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB123" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC123" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -21600,17 +21686,17 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -21644,170 +21730,81 @@
         </is>
       </c>
       <c r="N124" t="n">
+        <v>2</v>
+      </c>
+      <c r="O124" t="n">
+        <v>2</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.003875939847584092</v>
+      </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO124" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP124" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR124" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS124" t="inlineStr"/>
+      <c r="AT124" t="n">
         <v>0</v>
       </c>
-      <c r="O124" t="n">
-        <v>0</v>
-      </c>
-      <c r="U124" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V124" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W124" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X124" t="inlineStr">
-        <is>
-          <t>Meslinger</t>
-        </is>
-      </c>
-      <c r="Y124" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z124" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA124" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB124" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD124" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE124" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF124" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG124" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH124" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI124" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ124" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK124" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM124" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN124" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO124" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP124" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ124" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS124" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AT124" t="n">
-        <v>1</v>
-      </c>
       <c r="AU124" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV124" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA124" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB124" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC124" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -21839,12 +21836,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -21893,7 +21890,7 @@
       </c>
       <c r="U125" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_MEASLES</t>
+          <t>SER_NO_FHI_107_MONTHLY</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -21918,7 +21915,7 @@
       </c>
       <c r="AS125" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_MEASLES</t>
+          <t>SER_NO_FHI_107_MONTHLY</t>
         </is>
       </c>
       <c r="AT125" t="n">
@@ -21931,42 +21928,42 @@
       </c>
       <c r="AV125" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA125" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB125" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC125" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -21998,12 +21995,12 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -22044,22 +22041,22 @@
       </c>
       <c r="U126" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_MEASLES</t>
+          <t>SER_NO_FHI_107_MONTHLY</t>
         </is>
       </c>
       <c r="V126" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_MEASLES</t>
+          <t>SER_NO_FHI_107_MONTHLY</t>
         </is>
       </c>
       <c r="W126" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X126" t="inlineStr">
         <is>
-          <t>Mässling</t>
+          <t>Meslinger</t>
         </is>
       </c>
       <c r="Y126" t="inlineStr">
@@ -22084,7 +22081,7 @@
       </c>
       <c r="AC126" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD126" t="inlineStr">
@@ -22119,17 +22116,17 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK126" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
       <c r="AM126" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN126" t="b">
@@ -22152,7 +22149,7 @@
       </c>
       <c r="AS126" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_MEASLES</t>
+          <t>SER_NO_FHI_107_MONTHLY</t>
         </is>
       </c>
       <c r="AT126" t="n">
@@ -22165,42 +22162,42 @@
       </c>
       <c r="AV126" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA126" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB126" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC126" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -22232,12 +22229,12 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -22262,7 +22259,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -22271,81 +22268,95 @@
         </is>
       </c>
       <c r="N127" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O127" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R127" t="n">
-        <v>0.004900850445394598</v>
+        <v>0</v>
       </c>
       <c r="S127" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MEASLES</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO127" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP127" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR127" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS127" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ127" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS127" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MEASLES</t>
+        </is>
+      </c>
       <c r="AT127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU127" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV127" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA127" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB127" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC127" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -22372,17 +22383,17 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -22407,7 +22418,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
@@ -22416,81 +22427,170 @@
         </is>
       </c>
       <c r="N128" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O128" t="n">
-        <v>3</v>
-      </c>
-      <c r="R128" t="n">
-        <v>0.002450425222697299</v>
-      </c>
-      <c r="S128" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MEASLES</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MEASLES</t>
+        </is>
+      </c>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X128" t="inlineStr">
+        <is>
+          <t>Mässling</t>
+        </is>
+      </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z128" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB128" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC128" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD128" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE128" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF128" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG128" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH128" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI128" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ128" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK128" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM128" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN128" t="b">
+        <v>1</v>
       </c>
       <c r="AO128" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP128" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR128" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS128" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ128" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS128" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MEASLES</t>
+        </is>
+      </c>
       <c r="AT128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU128" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV128" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA128" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB128" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC128" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -22552,7 +22652,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -22561,13 +22661,13 @@
         </is>
       </c>
       <c r="N129" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O129" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R129" t="n">
-        <v>0</v>
+        <v>0.004900850445394598</v>
       </c>
       <c r="S129" t="inlineStr">
         <is>
@@ -22697,7 +22797,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
@@ -22706,13 +22806,13 @@
         </is>
       </c>
       <c r="N130" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O130" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R130" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0.002450425222697299</v>
       </c>
       <c r="S130" t="inlineStr">
         <is>
@@ -22842,7 +22942,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -22957,12 +23057,12 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -22987,22 +23087,22 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R132" t="n">
-        <v>0</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S132" t="inlineStr">
         <is>
@@ -23035,42 +23135,42 @@
       </c>
       <c r="AV132" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA132" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB132" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC132" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -23102,12 +23202,12 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -23132,12 +23232,12 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N133" t="n">
@@ -23154,82 +23254,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U133" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_170</t>
-        </is>
-      </c>
-      <c r="AA133" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO133" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP133" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ133" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS133" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_170</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR133" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS133" t="inlineStr"/>
       <c r="AT133" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU133" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV133" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA133" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB133" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC133" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -23256,17 +23342,17 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -23305,165 +23391,76 @@
       <c r="O134" t="n">
         <v>0</v>
       </c>
-      <c r="U134" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_170</t>
-        </is>
-      </c>
-      <c r="V134" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_170</t>
-        </is>
-      </c>
-      <c r="W134" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X134" t="inlineStr">
-        <is>
-          <t>Cinderella disease</t>
-        </is>
-      </c>
-      <c r="Y134" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z134" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA134" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB134" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC134" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD134" t="inlineStr">
+      <c r="R134" t="n">
+        <v>0</v>
+      </c>
+      <c r="S134" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO134" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP134" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR134" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS134" t="inlineStr"/>
+      <c r="AT134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU134" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV134" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE134" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF134" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG134" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH134" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI134" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ134" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK134" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; The English cube mistranslates Finnish Tuhkarokko; source code 170 is measles.</t>
-        </is>
-      </c>
-      <c r="AM134" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN134" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO134" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP134" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ134" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS134" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_170</t>
-        </is>
-      </c>
-      <c r="AT134" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU134" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV134" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA134" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB134" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC134" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -23495,12 +23492,12 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -23547,68 +23544,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_170</t>
+        </is>
+      </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO135" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP135" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR135" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS135" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ135" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS135" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_170</t>
+        </is>
+      </c>
       <c r="AT135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU135" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV135" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA135" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB135" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC135" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -23635,17 +23646,17 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -23684,17 +23695,34 @@
       <c r="O136" t="n">
         <v>0</v>
       </c>
-      <c r="R136" t="n">
-        <v>0</v>
-      </c>
-      <c r="S136" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U136" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
+          <t>SER_FI_THL_TTR_170</t>
+        </is>
+      </c>
+      <c r="V136" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_170</t>
+        </is>
+      </c>
+      <c r="W136" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X136" t="inlineStr">
+        <is>
+          <t>Cinderella disease</t>
+        </is>
+      </c>
+      <c r="Y136" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z136" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -23702,6 +23730,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB136" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD136" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE136" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF136" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG136" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH136" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI136" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ136" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK136" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; The English cube mistranslates Finnish Tuhkarokko; source code 170 is measles.</t>
+        </is>
+      </c>
+      <c r="AM136" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN136" t="b">
+        <v>1</v>
+      </c>
       <c r="AO136" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -23714,12 +23800,12 @@
       </c>
       <c r="AQ136" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS136" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
+          <t>SER_FI_THL_TTR_170</t>
         </is>
       </c>
       <c r="AT136" t="n">
@@ -23727,47 +23813,47 @@
       </c>
       <c r="AU136" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV136" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA136" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB136" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC136" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -23794,17 +23880,17 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -23843,165 +23929,76 @@
       <c r="O137" t="n">
         <v>0</v>
       </c>
-      <c r="U137" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V137" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W137" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X137" t="inlineStr">
-        <is>
-          <t>Meslinger</t>
-        </is>
-      </c>
-      <c r="Y137" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z137" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA137" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB137" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC137" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD137" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE137" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF137" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG137" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH137" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI137" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ137" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK137" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM137" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN137" t="b">
-        <v>1</v>
+      <c r="R137" t="n">
+        <v>0</v>
+      </c>
+      <c r="S137" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO137" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP137" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ137" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS137" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR137" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS137" t="inlineStr"/>
       <c r="AT137" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU137" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV137" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA137" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB137" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC137" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -24033,118 +24030,511 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>D017</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>麻疹</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N138" t="n">
+        <v>0</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0</v>
+      </c>
+      <c r="S138" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_107_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO138" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP138" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ138" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS138" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_107_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT138" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU138" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV138" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW138" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX138" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY138" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA138" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB138" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC138" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>D017</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>measles</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>D017</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>麻疹</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N139" t="n">
+        <v>0</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0</v>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_107_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_107_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W139" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X139" t="inlineStr">
+        <is>
+          <t>Meslinger</t>
+        </is>
+      </c>
+      <c r="Y139" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z139" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB139" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD139" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE139" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF139" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG139" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH139" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI139" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ139" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK139" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM139" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN139" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO139" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP139" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ139" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS139" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_107_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT139" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU139" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV139" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW139" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX139" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY139" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA139" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB139" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC139" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>D017</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>measles</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
           <t>JP</t>
         </is>
       </c>
-      <c r="G138" t="inlineStr">
+      <c r="G140" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>D017</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>Measles</t>
-        </is>
-      </c>
-      <c r="J138" t="inlineStr">
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>D017</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
         <is>
           <t>麻疹</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr">
+      <c r="K140" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="L138" t="inlineStr">
+      <c r="L140" t="inlineStr">
         <is>
           <t>2026-08-02</t>
         </is>
       </c>
-      <c r="M138" t="inlineStr">
+      <c r="M140" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="N138" t="n">
+      <c r="N140" t="n">
         <v>1</v>
       </c>
-      <c r="O138" t="n">
+      <c r="O140" t="n">
         <v>1</v>
       </c>
-      <c r="R138" t="n">
+      <c r="R140" t="n">
         <v>0.0008168084075657662</v>
       </c>
-      <c r="S138" t="inlineStr">
+      <c r="S140" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO138" t="inlineStr">
+      <c r="AO140" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP138" t="inlineStr">
+      <c r="AP140" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR138" t="inlineStr">
+      <c r="AR140" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS138" t="inlineStr"/>
-      <c r="AT138" t="n">
+      <c r="AS140" t="inlineStr"/>
+      <c r="AT140" t="n">
         <v>0</v>
       </c>
-      <c r="AU138" t="inlineStr">
+      <c r="AU140" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV138" t="inlineStr">
+      <c r="AV140" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="AW138" t="inlineStr">
+      <c r="AW140" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="AX138" t="inlineStr">
+      <c r="AX140" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="AY138" t="inlineStr">
+      <c r="AY140" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="AZ138" t="inlineStr">
+      <c r="AZ140" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="BA138" t="inlineStr">
+      <c r="BA140" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="BB138" t="inlineStr">
+      <c r="BB140" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="BC138" t="inlineStr">
+      <c r="BC140" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -24266,7 +24656,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="10">
@@ -24276,7 +24666,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="11">
@@ -24296,7 +24686,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13">
@@ -24328,7 +24718,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1288</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d017/2026-2029.xlsx
+++ b/diseases/d017/2026-2029.xlsx
@@ -24540,6 +24540,151 @@
         </is>
       </c>
     </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>D017</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>measles</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>D017</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>麻疹</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N141" t="n">
+        <v>2</v>
+      </c>
+      <c r="O141" t="n">
+        <v>2</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.001633616815131532</v>
+      </c>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO141" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP141" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR141" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS141" t="inlineStr"/>
+      <c r="AT141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU141" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV141" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW141" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX141" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY141" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA141" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB141" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC141" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -24573,7 +24718,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
@@ -24656,7 +24801,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="10">
@@ -24666,7 +24811,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11">
@@ -24718,7 +24863,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1290</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d017/2026-2029.xlsx
+++ b/diseases/d017/2026-2029.xlsx
@@ -21298,12 +21298,12 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -21337,95 +21337,84 @@
         </is>
       </c>
       <c r="N122" t="n">
+        <v>60</v>
+      </c>
+      <c r="O122" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q122" t="n">
         <v>0</v>
       </c>
-      <c r="O122" t="n">
+      <c r="R122" t="n">
+        <v>0.004246542694163248</v>
+      </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO122" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP122" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR122" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS122" t="inlineStr"/>
+      <c r="AT122" t="n">
         <v>0</v>
       </c>
-      <c r="R122" t="n">
-        <v>0</v>
-      </c>
-      <c r="S122" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U122" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_170</t>
-        </is>
-      </c>
-      <c r="AA122" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO122" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP122" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ122" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS122" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_170</t>
-        </is>
-      </c>
-      <c r="AT122" t="n">
-        <v>1</v>
-      </c>
       <c r="AU122" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV122" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA122" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB122" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC122" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -21452,7 +21441,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -21501,98 +21490,23 @@
       <c r="O123" t="n">
         <v>0</v>
       </c>
+      <c r="R123" t="n">
+        <v>0</v>
+      </c>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U123" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_170</t>
         </is>
       </c>
-      <c r="V123" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_170</t>
-        </is>
-      </c>
-      <c r="W123" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X123" t="inlineStr">
-        <is>
-          <t>Cinderella disease</t>
-        </is>
-      </c>
-      <c r="Y123" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z123" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB123" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD123" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE123" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF123" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG123" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH123" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI123" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ123" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK123" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; The English cube mistranslates Finnish Tuhkarokko; source code 170 is measles.</t>
-        </is>
-      </c>
-      <c r="AM123" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN123" t="b">
-        <v>1</v>
       </c>
       <c r="AO123" t="inlineStr">
         <is>
@@ -21686,17 +21600,17 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -21730,81 +21644,170 @@
         </is>
       </c>
       <c r="N124" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O124" t="n">
-        <v>2</v>
-      </c>
-      <c r="R124" t="n">
-        <v>0.003875939847584092</v>
-      </c>
-      <c r="S124" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_170</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_170</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X124" t="inlineStr">
+        <is>
+          <t>Cinderella disease</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD124" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE124" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF124" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG124" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH124" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI124" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ124" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK124" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; The English cube mistranslates Finnish Tuhkarokko; source code 170 is measles.</t>
+        </is>
+      </c>
+      <c r="AM124" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN124" t="b">
+        <v>1</v>
       </c>
       <c r="AO124" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP124" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR124" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS124" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ124" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS124" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_170</t>
+        </is>
+      </c>
       <c r="AT124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU124" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV124" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA124" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB124" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC124" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -21836,12 +21839,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -21875,95 +21878,81 @@
         </is>
       </c>
       <c r="N125" t="n">
+        <v>2</v>
+      </c>
+      <c r="O125" t="n">
+        <v>2</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.003875939847584092</v>
+      </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO125" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP125" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR125" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS125" t="inlineStr"/>
+      <c r="AT125" t="n">
         <v>0</v>
       </c>
-      <c r="O125" t="n">
-        <v>0</v>
-      </c>
-      <c r="R125" t="n">
-        <v>0</v>
-      </c>
-      <c r="S125" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U125" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA125" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO125" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP125" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ125" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS125" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AT125" t="n">
-        <v>1</v>
-      </c>
       <c r="AU125" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV125" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA125" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB125" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC125" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -21990,7 +21979,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -22039,98 +22028,23 @@
       <c r="O126" t="n">
         <v>0</v>
       </c>
+      <c r="R126" t="n">
+        <v>0</v>
+      </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U126" t="inlineStr">
         <is>
           <t>SER_NO_FHI_107_MONTHLY</t>
         </is>
       </c>
-      <c r="V126" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W126" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X126" t="inlineStr">
-        <is>
-          <t>Meslinger</t>
-        </is>
-      </c>
-      <c r="Y126" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z126" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB126" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC126" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD126" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE126" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF126" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG126" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH126" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI126" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ126" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK126" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM126" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN126" t="b">
-        <v>1</v>
       </c>
       <c r="AO126" t="inlineStr">
         <is>
@@ -22224,17 +22138,17 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -22273,17 +22187,34 @@
       <c r="O127" t="n">
         <v>0</v>
       </c>
-      <c r="R127" t="n">
-        <v>0</v>
-      </c>
-      <c r="S127" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U127" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_MEASLES</t>
+          <t>SER_NO_FHI_107_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_107_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X127" t="inlineStr">
+        <is>
+          <t>Meslinger</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z127" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -22291,6 +22222,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB127" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD127" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE127" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF127" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG127" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH127" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI127" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ127" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK127" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM127" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN127" t="b">
+        <v>1</v>
+      </c>
       <c r="AO127" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -22308,7 +22297,7 @@
       </c>
       <c r="AS127" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_MEASLES</t>
+          <t>SER_NO_FHI_107_MONTHLY</t>
         </is>
       </c>
       <c r="AT127" t="n">
@@ -22321,42 +22310,42 @@
       </c>
       <c r="AV127" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA127" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB127" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC127" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -22383,7 +22372,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -22432,98 +22421,23 @@
       <c r="O128" t="n">
         <v>0</v>
       </c>
+      <c r="R128" t="n">
+        <v>0</v>
+      </c>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U128" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_MEASLES</t>
         </is>
       </c>
-      <c r="V128" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_MEASLES</t>
-        </is>
-      </c>
-      <c r="W128" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X128" t="inlineStr">
-        <is>
-          <t>Mässling</t>
-        </is>
-      </c>
-      <c r="Y128" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z128" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB128" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC128" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD128" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE128" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF128" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG128" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH128" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI128" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ128" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK128" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
-        </is>
-      </c>
-      <c r="AM128" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN128" t="b">
-        <v>1</v>
       </c>
       <c r="AO128" t="inlineStr">
         <is>
@@ -22617,17 +22531,17 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -22652,7 +22566,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -22661,81 +22575,170 @@
         </is>
       </c>
       <c r="N129" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O129" t="n">
-        <v>6</v>
-      </c>
-      <c r="R129" t="n">
-        <v>0.004900850445394598</v>
-      </c>
-      <c r="S129" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MEASLES</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MEASLES</t>
+        </is>
+      </c>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X129" t="inlineStr">
+        <is>
+          <t>Mässling</t>
+        </is>
+      </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB129" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD129" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE129" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF129" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG129" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH129" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI129" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ129" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK129" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM129" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN129" t="b">
+        <v>1</v>
       </c>
       <c r="AO129" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP129" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR129" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS129" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ129" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS129" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MEASLES</t>
+        </is>
+      </c>
       <c r="AT129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU129" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV129" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA129" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB129" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC129" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -22797,7 +22800,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
@@ -22806,13 +22809,13 @@
         </is>
       </c>
       <c r="N130" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O130" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R130" t="n">
-        <v>0.002450425222697299</v>
+        <v>0.004900850445394598</v>
       </c>
       <c r="S130" t="inlineStr">
         <is>
@@ -22942,7 +22945,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -22951,13 +22954,13 @@
         </is>
       </c>
       <c r="N131" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O131" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R131" t="n">
-        <v>0</v>
+        <v>0.002450425222697299</v>
       </c>
       <c r="S131" t="inlineStr">
         <is>
@@ -23087,7 +23090,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
@@ -23096,13 +23099,13 @@
         </is>
       </c>
       <c r="N132" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O132" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R132" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0</v>
       </c>
       <c r="S132" t="inlineStr">
         <is>
@@ -23232,7 +23235,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
@@ -23241,13 +23244,13 @@
         </is>
       </c>
       <c r="N133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R133" t="n">
-        <v>0</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S133" t="inlineStr">
         <is>
@@ -23347,12 +23350,12 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -23377,12 +23380,12 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N134" t="n">
@@ -23425,42 +23428,42 @@
       </c>
       <c r="AV134" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA134" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB134" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC134" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -23492,12 +23495,12 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -23544,82 +23547,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U135" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_170</t>
-        </is>
-      </c>
-      <c r="AA135" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO135" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP135" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ135" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS135" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_170</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR135" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS135" t="inlineStr"/>
       <c r="AT135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU135" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV135" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA135" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB135" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC135" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -23646,7 +23635,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -23695,98 +23684,23 @@
       <c r="O136" t="n">
         <v>0</v>
       </c>
+      <c r="R136" t="n">
+        <v>0</v>
+      </c>
+      <c r="S136" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U136" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_170</t>
         </is>
       </c>
-      <c r="V136" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_170</t>
-        </is>
-      </c>
-      <c r="W136" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X136" t="inlineStr">
-        <is>
-          <t>Cinderella disease</t>
-        </is>
-      </c>
-      <c r="Y136" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z136" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA136" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB136" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC136" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD136" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE136" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF136" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG136" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH136" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI136" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ136" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK136" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; The English cube mistranslates Finnish Tuhkarokko; source code 170 is measles.</t>
-        </is>
-      </c>
-      <c r="AM136" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN136" t="b">
-        <v>1</v>
       </c>
       <c r="AO136" t="inlineStr">
         <is>
@@ -23880,17 +23794,17 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -23929,76 +23843,165 @@
       <c r="O137" t="n">
         <v>0</v>
       </c>
-      <c r="R137" t="n">
-        <v>0</v>
-      </c>
-      <c r="S137" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_170</t>
+        </is>
+      </c>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_170</t>
+        </is>
+      </c>
+      <c r="W137" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X137" t="inlineStr">
+        <is>
+          <t>Cinderella disease</t>
+        </is>
+      </c>
+      <c r="Y137" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z137" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB137" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC137" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD137" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE137" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF137" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG137" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH137" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI137" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ137" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK137" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; The English cube mistranslates Finnish Tuhkarokko; source code 170 is measles.</t>
+        </is>
+      </c>
+      <c r="AM137" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN137" t="b">
+        <v>1</v>
       </c>
       <c r="AO137" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP137" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR137" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS137" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ137" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS137" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_170</t>
+        </is>
+      </c>
       <c r="AT137" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU137" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV137" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA137" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB137" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC137" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -24030,12 +24033,12 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -24082,82 +24085,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U138" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA138" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO138" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP138" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ138" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS138" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR138" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS138" t="inlineStr"/>
       <c r="AT138" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU138" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV138" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA138" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB138" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC138" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -24184,7 +24173,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -24233,98 +24222,23 @@
       <c r="O139" t="n">
         <v>0</v>
       </c>
+      <c r="R139" t="n">
+        <v>0</v>
+      </c>
+      <c r="S139" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U139" t="inlineStr">
         <is>
           <t>SER_NO_FHI_107_MONTHLY</t>
         </is>
       </c>
-      <c r="V139" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W139" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X139" t="inlineStr">
-        <is>
-          <t>Meslinger</t>
-        </is>
-      </c>
-      <c r="Y139" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z139" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA139" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB139" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC139" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD139" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE139" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF139" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG139" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH139" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI139" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ139" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK139" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM139" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN139" t="b">
-        <v>1</v>
       </c>
       <c r="AO139" t="inlineStr">
         <is>
@@ -24418,17 +24332,17 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -24453,7 +24367,7 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
@@ -24462,81 +24376,170 @@
         </is>
       </c>
       <c r="N140" t="n">
+        <v>0</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0</v>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_107_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V140" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_107_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W140" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X140" t="inlineStr">
+        <is>
+          <t>Meslinger</t>
+        </is>
+      </c>
+      <c r="Y140" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z140" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB140" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD140" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE140" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF140" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG140" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH140" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI140" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ140" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK140" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM140" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN140" t="b">
         <v>1</v>
       </c>
-      <c r="O140" t="n">
+      <c r="AO140" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP140" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ140" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS140" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_107_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT140" t="n">
         <v>1</v>
       </c>
-      <c r="R140" t="n">
-        <v>0.0008168084075657662</v>
-      </c>
-      <c r="S140" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO140" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP140" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR140" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS140" t="inlineStr"/>
-      <c r="AT140" t="n">
-        <v>0</v>
-      </c>
       <c r="AU140" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV140" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA140" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB140" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC140" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -24598,7 +24601,7 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
@@ -24607,13 +24610,13 @@
         </is>
       </c>
       <c r="N141" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O141" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R141" t="n">
-        <v>0.001633616815131532</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S141" t="inlineStr">
         <is>
@@ -24680,6 +24683,151 @@
         </is>
       </c>
       <c r="BC141" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>D017</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>measles</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>D017</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>麻疹</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N142" t="n">
+        <v>2</v>
+      </c>
+      <c r="O142" t="n">
+        <v>2</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.001633616815131532</v>
+      </c>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO142" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP142" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR142" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS142" t="inlineStr"/>
+      <c r="AT142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU142" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV142" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW142" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX142" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY142" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA142" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB142" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC142" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -24801,7 +24949,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="10">
@@ -24811,7 +24959,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="11">
@@ -24863,7 +25011,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1292</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d017/2026-2029.xlsx
+++ b/diseases/d017/2026-2029.xlsx
@@ -22377,12 +22377,12 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -22416,13 +22416,13 @@
         </is>
       </c>
       <c r="N128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R128" t="n">
-        <v>0</v>
+        <v>0.01891260466471829</v>
       </c>
       <c r="S128" t="inlineStr">
         <is>
@@ -22431,7 +22431,7 @@
       </c>
       <c r="U128" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_MEASLES</t>
+          <t>SER_NZ_MEASLES_MONTHLY</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -22456,7 +22456,7 @@
       </c>
       <c r="AS128" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_MEASLES</t>
+          <t>SER_NZ_MEASLES_MONTHLY</t>
         </is>
       </c>
       <c r="AT128" t="n">
@@ -22469,42 +22469,42 @@
       </c>
       <c r="AV128" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA128" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB128" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC128" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -22536,12 +22536,12 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -22575,29 +22575,29 @@
         </is>
       </c>
       <c r="N129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U129" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_MEASLES</t>
+          <t>SER_NZ_MEASLES_MONTHLY</t>
         </is>
       </c>
       <c r="V129" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_MEASLES</t>
+          <t>SER_NZ_MEASLES_MONTHLY</t>
         </is>
       </c>
       <c r="W129" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NZ_PHS</t>
         </is>
       </c>
       <c r="X129" t="inlineStr">
         <is>
-          <t>Mässling</t>
+          <t>Measles</t>
         </is>
       </c>
       <c r="Y129" t="inlineStr">
@@ -22607,7 +22607,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -22622,7 +22622,7 @@
       </c>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NZ:national</t>
         </is>
       </c>
       <c r="AD129" t="inlineStr">
@@ -22657,17 +22657,17 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NZ_PHS_current</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+          <t>New Zealand PHF Science monthly measles notifications.</t>
         </is>
       </c>
       <c r="AM129" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN129" t="b">
@@ -22690,7 +22690,7 @@
       </c>
       <c r="AS129" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_MEASLES</t>
+          <t>SER_NZ_MEASLES_MONTHLY</t>
         </is>
       </c>
       <c r="AT129" t="n">
@@ -22703,42 +22703,42 @@
       </c>
       <c r="AV129" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA129" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB129" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC129" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -22770,12 +22770,12 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -22800,7 +22800,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
@@ -22809,81 +22809,95 @@
         </is>
       </c>
       <c r="N130" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O130" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R130" t="n">
-        <v>0.004900850445394598</v>
+        <v>0</v>
       </c>
       <c r="S130" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MEASLES</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO130" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP130" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR130" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS130" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ130" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS130" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MEASLES</t>
+        </is>
+      </c>
       <c r="AT130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU130" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV130" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA130" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB130" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC130" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -22910,17 +22924,17 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -22945,7 +22959,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -22954,81 +22968,170 @@
         </is>
       </c>
       <c r="N131" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O131" t="n">
-        <v>3</v>
-      </c>
-      <c r="R131" t="n">
-        <v>0.002450425222697299</v>
-      </c>
-      <c r="S131" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MEASLES</t>
+        </is>
+      </c>
+      <c r="V131" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MEASLES</t>
+        </is>
+      </c>
+      <c r="W131" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X131" t="inlineStr">
+        <is>
+          <t>Mässling</t>
+        </is>
+      </c>
+      <c r="Y131" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z131" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB131" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD131" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE131" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF131" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG131" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH131" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI131" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ131" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK131" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM131" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN131" t="b">
+        <v>1</v>
       </c>
       <c r="AO131" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP131" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR131" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS131" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ131" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS131" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MEASLES</t>
+        </is>
+      </c>
       <c r="AT131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU131" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV131" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA131" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB131" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC131" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -23090,7 +23193,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
@@ -23099,13 +23202,13 @@
         </is>
       </c>
       <c r="N132" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O132" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R132" t="n">
-        <v>0</v>
+        <v>0.004900850445394598</v>
       </c>
       <c r="S132" t="inlineStr">
         <is>
@@ -23235,7 +23338,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
@@ -23244,13 +23347,13 @@
         </is>
       </c>
       <c r="N133" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O133" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R133" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0.002450425222697299</v>
       </c>
       <c r="S133" t="inlineStr">
         <is>
@@ -23380,7 +23483,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
@@ -23495,12 +23598,12 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -23525,22 +23628,22 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R135" t="n">
-        <v>0</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S135" t="inlineStr">
         <is>
@@ -23573,42 +23676,42 @@
       </c>
       <c r="AV135" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA135" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB135" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC135" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -23640,12 +23743,12 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -23670,12 +23773,12 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N136" t="n">
@@ -23692,82 +23795,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U136" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_170</t>
-        </is>
-      </c>
-      <c r="AA136" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO136" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP136" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ136" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS136" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_170</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR136" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS136" t="inlineStr"/>
       <c r="AT136" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU136" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV136" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA136" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB136" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC136" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -23794,17 +23883,17 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -23843,165 +23932,76 @@
       <c r="O137" t="n">
         <v>0</v>
       </c>
-      <c r="U137" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_170</t>
-        </is>
-      </c>
-      <c r="V137" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_170</t>
-        </is>
-      </c>
-      <c r="W137" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X137" t="inlineStr">
-        <is>
-          <t>Cinderella disease</t>
-        </is>
-      </c>
-      <c r="Y137" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z137" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA137" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB137" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC137" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD137" t="inlineStr">
+      <c r="R137" t="n">
+        <v>0</v>
+      </c>
+      <c r="S137" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO137" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP137" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR137" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS137" t="inlineStr"/>
+      <c r="AT137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU137" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV137" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE137" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF137" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG137" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH137" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI137" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ137" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK137" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; The English cube mistranslates Finnish Tuhkarokko; source code 170 is measles.</t>
-        </is>
-      </c>
-      <c r="AM137" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN137" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO137" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP137" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ137" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS137" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_170</t>
-        </is>
-      </c>
-      <c r="AT137" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU137" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV137" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA137" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB137" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC137" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -24033,12 +24033,12 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -24085,68 +24085,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_170</t>
+        </is>
+      </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO138" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP138" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR138" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS138" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ138" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS138" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_170</t>
+        </is>
+      </c>
       <c r="AT138" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU138" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV138" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA138" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB138" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC138" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -24173,17 +24187,17 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -24222,17 +24236,34 @@
       <c r="O139" t="n">
         <v>0</v>
       </c>
-      <c r="R139" t="n">
-        <v>0</v>
-      </c>
-      <c r="S139" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U139" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
+          <t>SER_FI_THL_TTR_170</t>
+        </is>
+      </c>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_170</t>
+        </is>
+      </c>
+      <c r="W139" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X139" t="inlineStr">
+        <is>
+          <t>Cinderella disease</t>
+        </is>
+      </c>
+      <c r="Y139" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z139" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -24240,6 +24271,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB139" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD139" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE139" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF139" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG139" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH139" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI139" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ139" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK139" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; The English cube mistranslates Finnish Tuhkarokko; source code 170 is measles.</t>
+        </is>
+      </c>
+      <c r="AM139" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN139" t="b">
+        <v>1</v>
+      </c>
       <c r="AO139" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -24252,12 +24341,12 @@
       </c>
       <c r="AQ139" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS139" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
+          <t>SER_FI_THL_TTR_170</t>
         </is>
       </c>
       <c r="AT139" t="n">
@@ -24265,47 +24354,47 @@
       </c>
       <c r="AU139" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV139" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA139" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB139" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC139" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -24332,17 +24421,17 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -24381,165 +24470,76 @@
       <c r="O140" t="n">
         <v>0</v>
       </c>
-      <c r="U140" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V140" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W140" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X140" t="inlineStr">
-        <is>
-          <t>Meslinger</t>
-        </is>
-      </c>
-      <c r="Y140" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z140" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA140" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB140" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC140" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD140" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE140" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF140" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG140" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH140" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI140" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ140" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK140" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM140" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN140" t="b">
-        <v>1</v>
+      <c r="R140" t="n">
+        <v>0</v>
+      </c>
+      <c r="S140" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO140" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP140" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ140" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS140" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR140" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS140" t="inlineStr"/>
       <c r="AT140" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU140" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV140" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA140" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB140" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC140" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -24571,12 +24571,12 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -24601,7 +24601,7 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
@@ -24610,81 +24610,95 @@
         </is>
       </c>
       <c r="N141" t="n">
+        <v>0</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0</v>
+      </c>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_107_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO141" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP141" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ141" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS141" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_107_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT141" t="n">
         <v>1</v>
       </c>
-      <c r="O141" t="n">
-        <v>1</v>
-      </c>
-      <c r="R141" t="n">
-        <v>0.0008168084075657662</v>
-      </c>
-      <c r="S141" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO141" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP141" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR141" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS141" t="inlineStr"/>
-      <c r="AT141" t="n">
-        <v>0</v>
-      </c>
       <c r="AU141" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV141" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA141" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB141" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC141" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -24711,123 +24725,647 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>D017</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>麻疹</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N142" t="n">
+        <v>0</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0</v>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_107_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_107_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W142" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X142" t="inlineStr">
+        <is>
+          <t>Meslinger</t>
+        </is>
+      </c>
+      <c r="Y142" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z142" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB142" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD142" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE142" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF142" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG142" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH142" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI142" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ142" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK142" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM142" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN142" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO142" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP142" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ142" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS142" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_107_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT142" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU142" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV142" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW142" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX142" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY142" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA142" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB142" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC142" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>D017</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>measles</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
           <t>public_projection</t>
         </is>
       </c>
-      <c r="F142" t="inlineStr">
+      <c r="F143" t="inlineStr">
         <is>
           <t>JP</t>
         </is>
       </c>
-      <c r="G142" t="inlineStr">
+      <c r="G143" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>D017</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr">
-        <is>
-          <t>Measles</t>
-        </is>
-      </c>
-      <c r="J142" t="inlineStr">
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>D017</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
         <is>
           <t>麻疹</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr">
+      <c r="K143" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="L142" t="inlineStr">
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N143" t="n">
+        <v>1</v>
+      </c>
+      <c r="O143" t="n">
+        <v>1</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO143" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP143" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR143" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS143" t="inlineStr"/>
+      <c r="AT143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU143" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV143" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW143" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX143" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY143" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA143" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB143" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC143" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>D017</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>measles</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>D017</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>麻疹</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
         <is>
           <t>2026-08-09</t>
         </is>
       </c>
-      <c r="M142" t="inlineStr">
+      <c r="M144" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="N142" t="n">
+      <c r="N144" t="n">
         <v>2</v>
       </c>
-      <c r="O142" t="n">
+      <c r="O144" t="n">
         <v>2</v>
       </c>
-      <c r="R142" t="n">
+      <c r="R144" t="n">
         <v>0.001633616815131532</v>
       </c>
-      <c r="S142" t="inlineStr">
+      <c r="S144" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO142" t="inlineStr">
+      <c r="AO144" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP142" t="inlineStr">
+      <c r="AP144" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR142" t="inlineStr">
+      <c r="AR144" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS142" t="inlineStr"/>
-      <c r="AT142" t="n">
+      <c r="AS144" t="inlineStr"/>
+      <c r="AT144" t="n">
         <v>0</v>
       </c>
-      <c r="AU142" t="inlineStr">
+      <c r="AU144" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV142" t="inlineStr">
+      <c r="AV144" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="AW142" t="inlineStr">
+      <c r="AW144" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="AX142" t="inlineStr">
+      <c r="AX144" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="AY142" t="inlineStr">
+      <c r="AY144" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="AZ142" t="inlineStr">
+      <c r="AZ144" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="BA142" t="inlineStr">
+      <c r="BA144" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="BB142" t="inlineStr">
+      <c r="BB144" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="BC142" t="inlineStr">
+      <c r="BC144" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>D017</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>measles</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>D017</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>麻疹</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N145" t="n">
+        <v>0</v>
+      </c>
+      <c r="O145" t="n">
+        <v>0</v>
+      </c>
+      <c r="R145" t="n">
+        <v>0</v>
+      </c>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO145" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP145" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR145" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS145" t="inlineStr"/>
+      <c r="AT145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU145" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV145" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW145" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX145" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY145" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA145" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB145" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC145" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -24866,7 +25404,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -24949,7 +25487,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="10">
@@ -24959,7 +25497,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11">
@@ -24979,7 +25517,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13">
@@ -25011,7 +25549,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1352</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d017/2026-2029.xlsx
+++ b/diseases/d017/2026-2029.xlsx
@@ -32083,12 +32083,12 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -32122,13 +32122,13 @@
         </is>
       </c>
       <c r="N177" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O177" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R177" t="n">
-        <v>0.003875939847584092</v>
+        <v>0</v>
       </c>
       <c r="S177" t="inlineStr">
         <is>
@@ -32161,42 +32161,42 @@
       </c>
       <c r="AV177" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ177" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA177" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB177" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC177" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -32228,12 +32228,12 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -32267,95 +32267,81 @@
         </is>
       </c>
       <c r="N178" t="n">
+        <v>2</v>
+      </c>
+      <c r="O178" t="n">
+        <v>2</v>
+      </c>
+      <c r="R178" t="n">
+        <v>0.003875939847584092</v>
+      </c>
+      <c r="S178" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO178" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP178" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR178" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS178" t="inlineStr"/>
+      <c r="AT178" t="n">
         <v>0</v>
       </c>
-      <c r="O178" t="n">
-        <v>0</v>
-      </c>
-      <c r="R178" t="n">
-        <v>0</v>
-      </c>
-      <c r="S178" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U178" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA178" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO178" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP178" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ178" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS178" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AT178" t="n">
-        <v>1</v>
-      </c>
       <c r="AU178" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV178" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ178" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA178" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB178" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC178" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -32382,7 +32368,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -32431,98 +32417,23 @@
       <c r="O179" t="n">
         <v>0</v>
       </c>
+      <c r="R179" t="n">
+        <v>0</v>
+      </c>
+      <c r="S179" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U179" t="inlineStr">
         <is>
           <t>SER_NO_FHI_107_MONTHLY</t>
         </is>
       </c>
-      <c r="V179" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W179" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X179" t="inlineStr">
-        <is>
-          <t>Meslinger</t>
-        </is>
-      </c>
-      <c r="Y179" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z179" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA179" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB179" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC179" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD179" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE179" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF179" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG179" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH179" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI179" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ179" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK179" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM179" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN179" t="b">
-        <v>1</v>
       </c>
       <c r="AO179" t="inlineStr">
         <is>
@@ -32616,17 +32527,17 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -32660,29 +32571,104 @@
         </is>
       </c>
       <c r="N180" t="n">
+        <v>0</v>
+      </c>
+      <c r="O180" t="n">
+        <v>0</v>
+      </c>
+      <c r="U180" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_107_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V180" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_107_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W180" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X180" t="inlineStr">
+        <is>
+          <t>Meslinger</t>
+        </is>
+      </c>
+      <c r="Y180" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z180" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA180" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB180" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC180" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD180" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE180" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF180" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG180" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH180" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI180" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ180" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK180" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM180" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN180" t="b">
         <v>1</v>
       </c>
-      <c r="O180" t="n">
-        <v>1</v>
-      </c>
-      <c r="R180" t="n">
-        <v>0.01891260466471829</v>
-      </c>
-      <c r="S180" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U180" t="inlineStr">
-        <is>
-          <t>SER_NZ_MEASLES_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA180" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO180" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -32700,7 +32686,7 @@
       </c>
       <c r="AS180" t="inlineStr">
         <is>
-          <t>SER_NZ_MEASLES_MONTHLY</t>
+          <t>SER_NO_FHI_107_MONTHLY</t>
         </is>
       </c>
       <c r="AT180" t="n">
@@ -32713,42 +32699,42 @@
       </c>
       <c r="AV180" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ180" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA180" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB180" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC180" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -32775,7 +32761,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -32824,98 +32810,23 @@
       <c r="O181" t="n">
         <v>1</v>
       </c>
+      <c r="R181" t="n">
+        <v>0.01891260466471829</v>
+      </c>
+      <c r="S181" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U181" t="inlineStr">
         <is>
           <t>SER_NZ_MEASLES_MONTHLY</t>
         </is>
       </c>
-      <c r="V181" t="inlineStr">
-        <is>
-          <t>SER_NZ_MEASLES_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W181" t="inlineStr">
-        <is>
-          <t>SRC_NZ_PHS</t>
-        </is>
-      </c>
-      <c r="X181" t="inlineStr">
-        <is>
-          <t>Measles</t>
-        </is>
-      </c>
-      <c r="Y181" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z181" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA181" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB181" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC181" t="inlineStr">
-        <is>
-          <t>country:NZ:national</t>
-        </is>
-      </c>
-      <c r="AD181" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE181" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF181" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG181" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH181" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI181" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ181" t="inlineStr">
-        <is>
-          <t>NZ_PHS_current</t>
-        </is>
-      </c>
-      <c r="AK181" t="inlineStr">
-        <is>
-          <t>New Zealand PHF Science monthly measles notifications.</t>
-        </is>
-      </c>
-      <c r="AM181" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN181" t="b">
-        <v>1</v>
       </c>
       <c r="AO181" t="inlineStr">
         <is>
@@ -33009,17 +32920,17 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -33053,22 +32964,39 @@
         </is>
       </c>
       <c r="N182" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O182" t="n">
-        <v>0</v>
-      </c>
-      <c r="R182" t="n">
-        <v>0</v>
-      </c>
-      <c r="S182" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="U182" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_MEASLES</t>
+          <t>SER_NZ_MEASLES_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V182" t="inlineStr">
+        <is>
+          <t>SER_NZ_MEASLES_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W182" t="inlineStr">
+        <is>
+          <t>SRC_NZ_PHS</t>
+        </is>
+      </c>
+      <c r="X182" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="Y182" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z182" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
@@ -33076,6 +33004,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB182" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC182" t="inlineStr">
+        <is>
+          <t>country:NZ:national</t>
+        </is>
+      </c>
+      <c r="AD182" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE182" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF182" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG182" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH182" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI182" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ182" t="inlineStr">
+        <is>
+          <t>NZ_PHS_current</t>
+        </is>
+      </c>
+      <c r="AK182" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science monthly measles notifications.</t>
+        </is>
+      </c>
+      <c r="AM182" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN182" t="b">
+        <v>1</v>
+      </c>
       <c r="AO182" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -33093,7 +33079,7 @@
       </c>
       <c r="AS182" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_MEASLES</t>
+          <t>SER_NZ_MEASLES_MONTHLY</t>
         </is>
       </c>
       <c r="AT182" t="n">
@@ -33106,42 +33092,42 @@
       </c>
       <c r="AV182" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ182" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA182" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB182" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC182" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -33168,7 +33154,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -33217,98 +33203,23 @@
       <c r="O183" t="n">
         <v>0</v>
       </c>
+      <c r="R183" t="n">
+        <v>0</v>
+      </c>
+      <c r="S183" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U183" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_MEASLES</t>
         </is>
       </c>
-      <c r="V183" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_MEASLES</t>
-        </is>
-      </c>
-      <c r="W183" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X183" t="inlineStr">
-        <is>
-          <t>Mässling</t>
-        </is>
-      </c>
-      <c r="Y183" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z183" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA183" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB183" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC183" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD183" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE183" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF183" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG183" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH183" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI183" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ183" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK183" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
-        </is>
-      </c>
-      <c r="AM183" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN183" t="b">
-        <v>1</v>
       </c>
       <c r="AO183" t="inlineStr">
         <is>
@@ -33402,17 +33313,17 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -33437,7 +33348,7 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
@@ -33446,81 +33357,170 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O184" t="n">
-        <v>6</v>
-      </c>
-      <c r="R184" t="n">
-        <v>0.004900850445394598</v>
-      </c>
-      <c r="S184" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="U184" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MEASLES</t>
+        </is>
+      </c>
+      <c r="V184" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MEASLES</t>
+        </is>
+      </c>
+      <c r="W184" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X184" t="inlineStr">
+        <is>
+          <t>Mässling</t>
+        </is>
+      </c>
+      <c r="Y184" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z184" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA184" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB184" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC184" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD184" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE184" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF184" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG184" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH184" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI184" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ184" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK184" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM184" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN184" t="b">
+        <v>1</v>
       </c>
       <c r="AO184" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP184" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR184" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS184" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ184" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS184" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MEASLES</t>
+        </is>
+      </c>
       <c r="AT184" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU184" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV184" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ184" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA184" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB184" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC184" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -33552,12 +33552,12 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -33582,7 +33582,7 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
@@ -33591,93 +33591,81 @@
         </is>
       </c>
       <c r="N185" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O185" t="n">
-        <v>1</v>
-      </c>
-      <c r="P185" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="R185" t="n">
-        <v>0.01693265755097047</v>
+        <v>0.004900850445394598</v>
       </c>
       <c r="S185" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA185" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO185" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP185" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ185" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS185" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MEASLES; SER_SG_HIST_MEASLES</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR185" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS185" t="inlineStr"/>
       <c r="AT185" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU185" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV185" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ185" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA185" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB185" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC185" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -33704,7 +33692,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -33756,98 +33744,18 @@
       <c r="P186" t="n">
         <v>1</v>
       </c>
-      <c r="U186" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MEASLES</t>
-        </is>
-      </c>
-      <c r="V186" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MEASLES</t>
-        </is>
-      </c>
-      <c r="W186" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X186" t="inlineStr">
-        <is>
-          <t>Measles</t>
-        </is>
-      </c>
-      <c r="Y186" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z186" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R186" t="n">
+        <v>0.01693265755097047</v>
+      </c>
+      <c r="S186" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB186" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC186" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD186" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE186" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF186" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG186" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH186" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI186" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ186" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK186" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM186" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN186" t="b">
-        <v>1</v>
       </c>
       <c r="AO186" t="inlineStr">
         <is>
@@ -33941,17 +33849,17 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -33976,7 +33884,7 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
@@ -33985,81 +33893,173 @@
         </is>
       </c>
       <c r="N187" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O187" t="n">
-        <v>3</v>
-      </c>
-      <c r="R187" t="n">
-        <v>0.002450425222697299</v>
-      </c>
-      <c r="S187" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="P187" t="n">
+        <v>1</v>
+      </c>
+      <c r="U187" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MEASLES</t>
+        </is>
+      </c>
+      <c r="V187" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MEASLES</t>
+        </is>
+      </c>
+      <c r="W187" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X187" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="Y187" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z187" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA187" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB187" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC187" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD187" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE187" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF187" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG187" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH187" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI187" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ187" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK187" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM187" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN187" t="b">
+        <v>1</v>
       </c>
       <c r="AO187" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP187" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR187" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS187" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ187" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS187" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MEASLES; SER_SG_HIST_MEASLES</t>
+        </is>
+      </c>
       <c r="AT187" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU187" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV187" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ187" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA187" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB187" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC187" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -34091,12 +34091,12 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -34121,7 +34121,7 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
@@ -34130,93 +34130,81 @@
         </is>
       </c>
       <c r="N188" t="n">
+        <v>3</v>
+      </c>
+      <c r="O188" t="n">
+        <v>3</v>
+      </c>
+      <c r="R188" t="n">
+        <v>0.002450425222697299</v>
+      </c>
+      <c r="S188" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO188" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP188" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR188" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS188" t="inlineStr"/>
+      <c r="AT188" t="n">
         <v>0</v>
       </c>
-      <c r="O188" t="n">
-        <v>0</v>
-      </c>
-      <c r="P188" t="n">
-        <v>0</v>
-      </c>
-      <c r="R188" t="n">
-        <v>0</v>
-      </c>
-      <c r="S188" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA188" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AO188" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP188" t="inlineStr">
-        <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ188" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS188" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MEASLES; SER_SG_HIST_MEASLES</t>
-        </is>
-      </c>
-      <c r="AT188" t="n">
-        <v>2</v>
-      </c>
       <c r="AU188" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV188" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ188" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA188" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB188" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC188" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -34243,7 +34231,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -34295,98 +34283,18 @@
       <c r="P189" t="n">
         <v>0</v>
       </c>
-      <c r="U189" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MEASLES</t>
-        </is>
-      </c>
-      <c r="V189" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MEASLES</t>
-        </is>
-      </c>
-      <c r="W189" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X189" t="inlineStr">
-        <is>
-          <t>Measles</t>
-        </is>
-      </c>
-      <c r="Y189" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z189" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R189" t="n">
+        <v>0</v>
+      </c>
+      <c r="S189" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB189" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC189" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD189" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE189" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF189" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG189" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH189" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI189" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ189" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK189" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM189" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN189" t="b">
-        <v>1</v>
       </c>
       <c r="AO189" t="inlineStr">
         <is>
@@ -34480,17 +34388,17 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -34515,7 +34423,7 @@
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="M190" t="inlineStr">
@@ -34529,76 +34437,168 @@
       <c r="O190" t="n">
         <v>0</v>
       </c>
-      <c r="R190" t="n">
+      <c r="P190" t="n">
         <v>0</v>
       </c>
-      <c r="S190" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U190" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MEASLES</t>
+        </is>
+      </c>
+      <c r="V190" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MEASLES</t>
+        </is>
+      </c>
+      <c r="W190" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X190" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="Y190" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z190" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA190" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB190" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC190" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD190" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE190" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF190" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG190" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH190" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI190" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ190" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK190" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM190" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN190" t="b">
+        <v>1</v>
       </c>
       <c r="AO190" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP190" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR190" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS190" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ190" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS190" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MEASLES; SER_SG_HIST_MEASLES</t>
+        </is>
+      </c>
       <c r="AT190" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU190" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV190" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ190" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA190" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB190" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC190" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -34630,12 +34630,12 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -34660,7 +34660,7 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
@@ -34669,93 +34669,81 @@
         </is>
       </c>
       <c r="N191" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O191" t="n">
-        <v>3</v>
-      </c>
-      <c r="P191" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R191" t="n">
-        <v>0.05079797265291142</v>
+        <v>0</v>
       </c>
       <c r="S191" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA191" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO191" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP191" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ191" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS191" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MEASLES; SER_SG_HIST_MEASLES</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR191" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS191" t="inlineStr"/>
       <c r="AT191" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU191" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV191" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ191" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA191" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB191" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC191" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -34782,7 +34770,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -34834,98 +34822,18 @@
       <c r="P192" t="n">
         <v>3</v>
       </c>
-      <c r="U192" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MEASLES</t>
-        </is>
-      </c>
-      <c r="V192" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MEASLES</t>
-        </is>
-      </c>
-      <c r="W192" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X192" t="inlineStr">
-        <is>
-          <t>Measles</t>
-        </is>
-      </c>
-      <c r="Y192" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z192" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R192" t="n">
+        <v>0.05079797265291142</v>
+      </c>
+      <c r="S192" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB192" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC192" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD192" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE192" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF192" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG192" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH192" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI192" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ192" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK192" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM192" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN192" t="b">
-        <v>1</v>
       </c>
       <c r="AO192" t="inlineStr">
         <is>
@@ -35019,17 +34927,17 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -35054,7 +34962,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
@@ -35063,81 +34971,173 @@
         </is>
       </c>
       <c r="N193" t="n">
+        <v>3</v>
+      </c>
+      <c r="O193" t="n">
+        <v>3</v>
+      </c>
+      <c r="P193" t="n">
+        <v>3</v>
+      </c>
+      <c r="U193" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MEASLES</t>
+        </is>
+      </c>
+      <c r="V193" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MEASLES</t>
+        </is>
+      </c>
+      <c r="W193" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X193" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="Y193" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z193" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA193" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB193" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC193" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD193" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE193" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF193" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG193" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH193" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI193" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ193" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK193" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM193" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN193" t="b">
         <v>1</v>
       </c>
-      <c r="O193" t="n">
-        <v>1</v>
-      </c>
-      <c r="R193" t="n">
-        <v>0.0008168084075657662</v>
-      </c>
-      <c r="S193" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AO193" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP193" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR193" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS193" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ193" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS193" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MEASLES; SER_SG_HIST_MEASLES</t>
+        </is>
+      </c>
       <c r="AT193" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU193" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV193" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ193" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA193" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB193" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC193" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -35199,7 +35199,7 @@
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M194" t="inlineStr">
@@ -35208,13 +35208,13 @@
         </is>
       </c>
       <c r="N194" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O194" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R194" t="n">
-        <v>0</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S194" t="inlineStr">
         <is>
@@ -35314,12 +35314,12 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -35358,9 +35358,6 @@
       <c r="O195" t="n">
         <v>0</v>
       </c>
-      <c r="P195" t="n">
-        <v>0</v>
-      </c>
       <c r="R195" t="n">
         <v>0</v>
       </c>
@@ -35369,77 +35366,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA195" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO195" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP195" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ195" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS195" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MEASLES; SER_SG_HIST_MEASLES</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR195" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS195" t="inlineStr"/>
       <c r="AT195" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU195" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV195" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ195" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA195" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB195" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC195" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -35466,7 +35454,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -35518,98 +35506,18 @@
       <c r="P196" t="n">
         <v>0</v>
       </c>
-      <c r="U196" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MEASLES</t>
-        </is>
-      </c>
-      <c r="V196" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MEASLES</t>
-        </is>
-      </c>
-      <c r="W196" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X196" t="inlineStr">
-        <is>
-          <t>Measles</t>
-        </is>
-      </c>
-      <c r="Y196" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z196" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R196" t="n">
+        <v>0</v>
+      </c>
+      <c r="S196" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB196" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC196" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD196" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE196" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF196" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG196" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH196" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI196" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ196" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK196" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM196" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN196" t="b">
-        <v>1</v>
       </c>
       <c r="AO196" t="inlineStr">
         <is>
@@ -35703,17 +35611,17 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -35738,12 +35646,12 @@
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N197" t="n">
@@ -35752,76 +35660,168 @@
       <c r="O197" t="n">
         <v>0</v>
       </c>
-      <c r="R197" t="n">
+      <c r="P197" t="n">
         <v>0</v>
       </c>
-      <c r="S197" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U197" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MEASLES</t>
+        </is>
+      </c>
+      <c r="V197" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MEASLES</t>
+        </is>
+      </c>
+      <c r="W197" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X197" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="Y197" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z197" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA197" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB197" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC197" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD197" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE197" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF197" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG197" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH197" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI197" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ197" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK197" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM197" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN197" t="b">
+        <v>1</v>
       </c>
       <c r="AO197" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP197" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR197" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS197" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ197" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS197" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MEASLES; SER_SG_HIST_MEASLES</t>
+        </is>
+      </c>
       <c r="AT197" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU197" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV197" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ197" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA197" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB197" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC197" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -35853,12 +35853,12 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -35905,82 +35905,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U198" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_170</t>
-        </is>
-      </c>
-      <c r="AA198" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO198" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP198" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ198" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS198" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_170</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR198" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS198" t="inlineStr"/>
       <c r="AT198" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU198" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV198" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ198" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA198" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB198" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC198" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -36007,7 +35993,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -36056,98 +36042,23 @@
       <c r="O199" t="n">
         <v>0</v>
       </c>
+      <c r="R199" t="n">
+        <v>0</v>
+      </c>
+      <c r="S199" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U199" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_170</t>
         </is>
       </c>
-      <c r="V199" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_170</t>
-        </is>
-      </c>
-      <c r="W199" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X199" t="inlineStr">
-        <is>
-          <t>Cinderella disease</t>
-        </is>
-      </c>
-      <c r="Y199" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z199" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA199" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB199" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC199" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD199" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE199" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF199" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG199" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH199" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI199" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ199" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK199" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; The English cube mistranslates Finnish Tuhkarokko; source code 170 is measles.</t>
-        </is>
-      </c>
-      <c r="AM199" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN199" t="b">
-        <v>1</v>
       </c>
       <c r="AO199" t="inlineStr">
         <is>
@@ -36241,17 +36152,17 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -36290,76 +36201,165 @@
       <c r="O200" t="n">
         <v>0</v>
       </c>
-      <c r="R200" t="n">
-        <v>0</v>
-      </c>
-      <c r="S200" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U200" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_170</t>
+        </is>
+      </c>
+      <c r="V200" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_170</t>
+        </is>
+      </c>
+      <c r="W200" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X200" t="inlineStr">
+        <is>
+          <t>Cinderella disease</t>
+        </is>
+      </c>
+      <c r="Y200" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z200" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA200" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB200" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC200" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD200" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE200" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF200" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG200" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH200" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI200" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ200" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK200" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; The English cube mistranslates Finnish Tuhkarokko; source code 170 is measles.</t>
+        </is>
+      </c>
+      <c r="AM200" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN200" t="b">
+        <v>1</v>
       </c>
       <c r="AO200" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP200" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR200" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS200" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ200" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS200" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_170</t>
+        </is>
+      </c>
       <c r="AT200" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU200" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV200" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ200" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA200" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB200" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC200" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -36391,12 +36391,12 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -36443,82 +36443,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U201" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA201" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO201" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP201" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ201" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS201" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR201" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS201" t="inlineStr"/>
       <c r="AT201" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU201" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV201" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ201" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA201" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB201" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC201" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -36545,7 +36531,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -36594,98 +36580,23 @@
       <c r="O202" t="n">
         <v>0</v>
       </c>
+      <c r="R202" t="n">
+        <v>0</v>
+      </c>
+      <c r="S202" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U202" t="inlineStr">
         <is>
           <t>SER_NO_FHI_107_MONTHLY</t>
         </is>
       </c>
-      <c r="V202" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W202" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X202" t="inlineStr">
-        <is>
-          <t>Meslinger</t>
-        </is>
-      </c>
-      <c r="Y202" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z202" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA202" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB202" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC202" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD202" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE202" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF202" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG202" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH202" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI202" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ202" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK202" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM202" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN202" t="b">
-        <v>1</v>
       </c>
       <c r="AO202" t="inlineStr">
         <is>
@@ -36779,17 +36690,17 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -36814,7 +36725,7 @@
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M203" t="inlineStr">
@@ -36823,81 +36734,170 @@
         </is>
       </c>
       <c r="N203" t="n">
+        <v>0</v>
+      </c>
+      <c r="O203" t="n">
+        <v>0</v>
+      </c>
+      <c r="U203" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_107_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V203" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_107_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W203" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X203" t="inlineStr">
+        <is>
+          <t>Meslinger</t>
+        </is>
+      </c>
+      <c r="Y203" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z203" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA203" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB203" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC203" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD203" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE203" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF203" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG203" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH203" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI203" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ203" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK203" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM203" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN203" t="b">
         <v>1</v>
       </c>
-      <c r="O203" t="n">
+      <c r="AO203" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP203" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ203" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS203" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_107_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT203" t="n">
         <v>1</v>
       </c>
-      <c r="R203" t="n">
-        <v>0.0008168084075657662</v>
-      </c>
-      <c r="S203" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO203" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP203" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR203" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS203" t="inlineStr"/>
-      <c r="AT203" t="n">
-        <v>0</v>
-      </c>
       <c r="AU203" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV203" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW203" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ203" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA203" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB203" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC203" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -36929,12 +36929,12 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -36968,93 +36968,81 @@
         </is>
       </c>
       <c r="N204" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O204" t="n">
-        <v>2</v>
-      </c>
-      <c r="P204" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R204" t="n">
-        <v>0.03386531510194095</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S204" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA204" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO204" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP204" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ204" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS204" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MEASLES; SER_SG_HIST_MEASLES</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR204" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS204" t="inlineStr"/>
       <c r="AT204" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU204" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV204" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW204" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY204" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ204" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA204" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB204" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC204" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -37081,7 +37069,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
@@ -37133,98 +37121,18 @@
       <c r="P205" t="n">
         <v>2</v>
       </c>
-      <c r="U205" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MEASLES</t>
-        </is>
-      </c>
-      <c r="V205" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MEASLES</t>
-        </is>
-      </c>
-      <c r="W205" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X205" t="inlineStr">
-        <is>
-          <t>Measles</t>
-        </is>
-      </c>
-      <c r="Y205" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z205" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R205" t="n">
+        <v>0.03386531510194095</v>
+      </c>
+      <c r="S205" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB205" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC205" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD205" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE205" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF205" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG205" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH205" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI205" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ205" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK205" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM205" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN205" t="b">
-        <v>1</v>
       </c>
       <c r="AO205" t="inlineStr">
         <is>
@@ -37318,17 +37226,17 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -37353,7 +37261,7 @@
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M206" t="inlineStr">
@@ -37367,76 +37275,168 @@
       <c r="O206" t="n">
         <v>2</v>
       </c>
-      <c r="R206" t="n">
-        <v>0.001633616815131532</v>
-      </c>
-      <c r="S206" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P206" t="n">
+        <v>2</v>
+      </c>
+      <c r="U206" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MEASLES</t>
+        </is>
+      </c>
+      <c r="V206" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MEASLES</t>
+        </is>
+      </c>
+      <c r="W206" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X206" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="Y206" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z206" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA206" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB206" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC206" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD206" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE206" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF206" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG206" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH206" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI206" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ206" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK206" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM206" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN206" t="b">
+        <v>1</v>
       </c>
       <c r="AO206" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP206" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR206" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS206" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ206" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS206" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MEASLES; SER_SG_HIST_MEASLES</t>
+        </is>
+      </c>
       <c r="AT206" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU206" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV206" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ206" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA206" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB206" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC206" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -37468,12 +37468,12 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -37507,93 +37507,81 @@
         </is>
       </c>
       <c r="N207" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O207" t="n">
-        <v>1</v>
-      </c>
-      <c r="P207" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R207" t="n">
-        <v>0.01693265755097047</v>
+        <v>0.001633616815131532</v>
       </c>
       <c r="S207" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA207" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO207" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP207" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ207" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS207" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MEASLES; SER_SG_HIST_MEASLES</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR207" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS207" t="inlineStr"/>
       <c r="AT207" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU207" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV207" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ207" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA207" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB207" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC207" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -37620,7 +37608,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -37672,98 +37660,18 @@
       <c r="P208" t="n">
         <v>1</v>
       </c>
-      <c r="U208" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MEASLES</t>
-        </is>
-      </c>
-      <c r="V208" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MEASLES</t>
-        </is>
-      </c>
-      <c r="W208" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X208" t="inlineStr">
-        <is>
-          <t>Measles</t>
-        </is>
-      </c>
-      <c r="Y208" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z208" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R208" t="n">
+        <v>0.01693265755097047</v>
+      </c>
+      <c r="S208" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB208" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC208" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD208" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE208" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF208" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG208" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH208" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI208" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ208" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK208" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM208" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN208" t="b">
-        <v>1</v>
       </c>
       <c r="AO208" t="inlineStr">
         <is>
@@ -37857,17 +37765,17 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -37892,7 +37800,7 @@
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M209" t="inlineStr">
@@ -37901,81 +37809,173 @@
         </is>
       </c>
       <c r="N209" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O209" t="n">
-        <v>0</v>
-      </c>
-      <c r="R209" t="n">
-        <v>0</v>
-      </c>
-      <c r="S209" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="P209" t="n">
+        <v>1</v>
+      </c>
+      <c r="U209" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MEASLES</t>
+        </is>
+      </c>
+      <c r="V209" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MEASLES</t>
+        </is>
+      </c>
+      <c r="W209" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X209" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="Y209" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z209" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA209" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB209" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC209" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD209" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE209" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF209" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG209" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH209" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI209" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ209" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK209" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM209" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN209" t="b">
+        <v>1</v>
       </c>
       <c r="AO209" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP209" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR209" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS209" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ209" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS209" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MEASLES; SER_SG_HIST_MEASLES</t>
+        </is>
+      </c>
       <c r="AT209" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU209" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV209" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW209" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX209" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY209" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ209" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA209" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB209" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC209" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -38007,12 +38007,12 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -38046,93 +38046,81 @@
         </is>
       </c>
       <c r="N210" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O210" t="n">
-        <v>2</v>
-      </c>
-      <c r="P210" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R210" t="n">
-        <v>0.03386531510194095</v>
+        <v>0</v>
       </c>
       <c r="S210" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA210" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO210" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP210" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ210" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS210" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MEASLES; SER_SG_HIST_MEASLES</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR210" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS210" t="inlineStr"/>
       <c r="AT210" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU210" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV210" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ210" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA210" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB210" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC210" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -38159,7 +38147,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
@@ -38211,98 +38199,18 @@
       <c r="P211" t="n">
         <v>2</v>
       </c>
-      <c r="U211" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MEASLES</t>
-        </is>
-      </c>
-      <c r="V211" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MEASLES</t>
-        </is>
-      </c>
-      <c r="W211" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X211" t="inlineStr">
-        <is>
-          <t>Measles</t>
-        </is>
-      </c>
-      <c r="Y211" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z211" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R211" t="n">
+        <v>0.03386531510194095</v>
+      </c>
+      <c r="S211" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB211" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC211" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD211" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE211" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF211" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG211" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH211" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI211" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ211" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK211" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM211" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN211" t="b">
-        <v>1</v>
       </c>
       <c r="AO211" t="inlineStr">
         <is>
@@ -38368,6 +38276,243 @@
         </is>
       </c>
       <c r="BC211" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>D017</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>measles</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>D017</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>麻疹</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N212" t="n">
+        <v>2</v>
+      </c>
+      <c r="O212" t="n">
+        <v>2</v>
+      </c>
+      <c r="P212" t="n">
+        <v>2</v>
+      </c>
+      <c r="U212" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MEASLES</t>
+        </is>
+      </c>
+      <c r="V212" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MEASLES</t>
+        </is>
+      </c>
+      <c r="W212" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X212" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="Y212" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z212" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA212" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB212" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC212" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD212" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE212" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF212" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG212" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH212" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI212" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ212" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK212" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM212" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN212" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO212" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP212" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ212" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS212" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MEASLES; SER_SG_HIST_MEASLES</t>
+        </is>
+      </c>
+      <c r="AT212" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU212" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV212" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW212" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX212" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY212" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ212" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA212" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB212" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC212" t="inlineStr">
         <is>
           <t>official_csv_and_workbook</t>
         </is>
@@ -38489,7 +38634,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="10">
@@ -38499,7 +38644,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d017/2026-2029.xlsx
+++ b/diseases/d017/2026-2029.xlsx
@@ -1621,7 +1621,7 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
@@ -1629,17 +1629,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS7" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_170</t>
         </is>
       </c>
       <c r="AT7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
@@ -1855,7 +1860,7 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
@@ -1863,17 +1868,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS8" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_170</t>
         </is>
       </c>
       <c r="AT8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
@@ -2304,7 +2314,7 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
@@ -2312,17 +2322,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS11" t="inlineStr">
         <is>
           <t>SER_NO_FHI_107_MONTHLY</t>
         </is>
       </c>
       <c r="AT11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
@@ -2538,7 +2553,7 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
@@ -2546,17 +2561,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS12" t="inlineStr">
         <is>
           <t>SER_NO_FHI_107_MONTHLY</t>
         </is>
       </c>
       <c r="AT12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
@@ -3093,7 +3113,7 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
@@ -3101,17 +3121,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS15" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_MEASLES</t>
         </is>
       </c>
       <c r="AT15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
@@ -3327,7 +3352,7 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
@@ -3335,17 +3360,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS16" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_MEASLES</t>
         </is>
       </c>
       <c r="AT16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
@@ -6485,7 +6515,7 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ34" t="inlineStr">
@@ -6493,17 +6523,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR34" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS34" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_170</t>
         </is>
       </c>
       <c r="AT34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV34" t="inlineStr">
@@ -6719,7 +6754,7 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ35" t="inlineStr">
@@ -6727,17 +6762,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR35" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS35" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_170</t>
         </is>
       </c>
       <c r="AT35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV35" t="inlineStr">
@@ -7168,7 +7208,7 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ38" t="inlineStr">
@@ -7176,17 +7216,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR38" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS38" t="inlineStr">
         <is>
           <t>SER_NO_FHI_107_MONTHLY</t>
         </is>
       </c>
       <c r="AT38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV38" t="inlineStr">
@@ -7402,7 +7447,7 @@
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ39" t="inlineStr">
@@ -7410,17 +7455,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR39" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS39" t="inlineStr">
         <is>
           <t>SER_NO_FHI_107_MONTHLY</t>
         </is>
       </c>
       <c r="AT39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV39" t="inlineStr">
@@ -7957,7 +8007,7 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ42" t="inlineStr">
@@ -7965,17 +8015,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR42" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS42" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_MEASLES</t>
         </is>
       </c>
       <c r="AT42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU42" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV42" t="inlineStr">
@@ -8191,7 +8246,7 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ43" t="inlineStr">
@@ -8199,17 +8254,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR43" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS43" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_MEASLES</t>
         </is>
       </c>
       <c r="AT43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU43" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV43" t="inlineStr">
@@ -11497,7 +11557,7 @@
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ62" t="inlineStr">
@@ -11505,17 +11565,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR62" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS62" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_170</t>
         </is>
       </c>
       <c r="AT62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU62" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV62" t="inlineStr">
@@ -11731,7 +11796,7 @@
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ63" t="inlineStr">
@@ -11739,17 +11804,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR63" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS63" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_170</t>
         </is>
       </c>
       <c r="AT63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU63" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV63" t="inlineStr">
@@ -12180,7 +12250,7 @@
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ66" t="inlineStr">
@@ -12188,17 +12258,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR66" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS66" t="inlineStr">
         <is>
           <t>SER_NO_FHI_107_MONTHLY</t>
         </is>
       </c>
       <c r="AT66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU66" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV66" t="inlineStr">
@@ -12414,7 +12489,7 @@
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ67" t="inlineStr">
@@ -12422,17 +12497,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR67" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS67" t="inlineStr">
         <is>
           <t>SER_NO_FHI_107_MONTHLY</t>
         </is>
       </c>
       <c r="AT67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU67" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV67" t="inlineStr">
@@ -12969,7 +13049,7 @@
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ70" t="inlineStr">
@@ -12977,17 +13057,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR70" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS70" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_MEASLES</t>
         </is>
       </c>
       <c r="AT70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU70" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV70" t="inlineStr">
@@ -13203,7 +13288,7 @@
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ71" t="inlineStr">
@@ -13211,17 +13296,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR71" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS71" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_MEASLES</t>
         </is>
       </c>
       <c r="AT71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU71" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV71" t="inlineStr">
@@ -16900,7 +16990,7 @@
       </c>
       <c r="AP92" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ92" t="inlineStr">
@@ -16908,17 +16998,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR92" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS92" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_170</t>
         </is>
       </c>
       <c r="AT92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU92" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV92" t="inlineStr">
@@ -17134,7 +17229,7 @@
       </c>
       <c r="AP93" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ93" t="inlineStr">
@@ -17142,17 +17237,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR93" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS93" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_170</t>
         </is>
       </c>
       <c r="AT93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU93" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV93" t="inlineStr">
@@ -17583,7 +17683,7 @@
       </c>
       <c r="AP96" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ96" t="inlineStr">
@@ -17591,17 +17691,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR96" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS96" t="inlineStr">
         <is>
           <t>SER_NO_FHI_107_MONTHLY</t>
         </is>
       </c>
       <c r="AT96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU96" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV96" t="inlineStr">
@@ -17817,7 +17922,7 @@
       </c>
       <c r="AP97" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ97" t="inlineStr">
@@ -17825,17 +17930,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR97" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS97" t="inlineStr">
         <is>
           <t>SER_NO_FHI_107_MONTHLY</t>
         </is>
       </c>
       <c r="AT97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU97" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV97" t="inlineStr">
@@ -18369,7 +18479,7 @@
       </c>
       <c r="AP100" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ100" t="inlineStr">
@@ -18377,17 +18487,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR100" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS100" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_MEASLES</t>
         </is>
       </c>
       <c r="AT100" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU100" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV100" t="inlineStr">
@@ -18603,7 +18718,7 @@
       </c>
       <c r="AP101" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ101" t="inlineStr">
@@ -18611,17 +18726,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR101" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS101" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_MEASLES</t>
         </is>
       </c>
       <c r="AT101" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU101" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV101" t="inlineStr">
@@ -21903,7 +22023,7 @@
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ120" t="inlineStr">
@@ -21911,17 +22031,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR120" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS120" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_170</t>
         </is>
       </c>
       <c r="AT120" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU120" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV120" t="inlineStr">
@@ -22137,7 +22262,7 @@
       </c>
       <c r="AP121" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ121" t="inlineStr">
@@ -22145,17 +22270,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR121" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS121" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_170</t>
         </is>
       </c>
       <c r="AT121" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU121" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV121" t="inlineStr">
@@ -22586,7 +22716,7 @@
       </c>
       <c r="AP124" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ124" t="inlineStr">
@@ -22594,17 +22724,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR124" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS124" t="inlineStr">
         <is>
           <t>SER_NO_FHI_107_MONTHLY</t>
         </is>
       </c>
       <c r="AT124" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU124" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV124" t="inlineStr">
@@ -22820,7 +22955,7 @@
       </c>
       <c r="AP125" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ125" t="inlineStr">
@@ -22828,17 +22963,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR125" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS125" t="inlineStr">
         <is>
           <t>SER_NO_FHI_107_MONTHLY</t>
         </is>
       </c>
       <c r="AT125" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU125" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV125" t="inlineStr">
@@ -23372,7 +23512,7 @@
       </c>
       <c r="AP128" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ128" t="inlineStr">
@@ -23380,17 +23520,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR128" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS128" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_MEASLES</t>
         </is>
       </c>
       <c r="AT128" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU128" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV128" t="inlineStr">
@@ -23606,7 +23751,7 @@
       </c>
       <c r="AP129" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ129" t="inlineStr">
@@ -23614,17 +23759,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR129" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS129" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_MEASLES</t>
         </is>
       </c>
       <c r="AT129" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU129" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV129" t="inlineStr">
@@ -27448,7 +27598,7 @@
       </c>
       <c r="AP151" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ151" t="inlineStr">
@@ -27456,17 +27606,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR151" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS151" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_170</t>
         </is>
       </c>
       <c r="AT151" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU151" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV151" t="inlineStr">
@@ -27682,7 +27837,7 @@
       </c>
       <c r="AP152" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ152" t="inlineStr">
@@ -27690,17 +27845,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR152" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS152" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_170</t>
         </is>
       </c>
       <c r="AT152" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU152" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV152" t="inlineStr">
@@ -28131,7 +28291,7 @@
       </c>
       <c r="AP155" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ155" t="inlineStr">
@@ -28139,17 +28299,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR155" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS155" t="inlineStr">
         <is>
           <t>SER_NO_FHI_107_MONTHLY</t>
         </is>
       </c>
       <c r="AT155" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU155" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV155" t="inlineStr">
@@ -28365,7 +28530,7 @@
       </c>
       <c r="AP156" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ156" t="inlineStr">
@@ -28373,17 +28538,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR156" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS156" t="inlineStr">
         <is>
           <t>SER_NO_FHI_107_MONTHLY</t>
         </is>
       </c>
       <c r="AT156" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU156" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV156" t="inlineStr">
@@ -28917,7 +29087,7 @@
       </c>
       <c r="AP159" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ159" t="inlineStr">
@@ -28925,17 +29095,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR159" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS159" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_MEASLES</t>
         </is>
       </c>
       <c r="AT159" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU159" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV159" t="inlineStr">
@@ -29151,7 +29326,7 @@
       </c>
       <c r="AP160" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ160" t="inlineStr">
@@ -29159,17 +29334,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR160" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS160" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_MEASLES</t>
         </is>
       </c>
       <c r="AT160" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU160" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV160" t="inlineStr">
@@ -31759,7 +31939,7 @@
       </c>
       <c r="AP175" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ175" t="inlineStr">
@@ -31767,17 +31947,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR175" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS175" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_170</t>
         </is>
       </c>
       <c r="AT175" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU175" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV175" t="inlineStr">
@@ -31993,7 +32178,7 @@
       </c>
       <c r="AP176" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ176" t="inlineStr">
@@ -32001,17 +32186,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR176" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS176" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_170</t>
         </is>
       </c>
       <c r="AT176" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU176" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV176" t="inlineStr">
@@ -32442,7 +32632,7 @@
       </c>
       <c r="AP179" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ179" t="inlineStr">
@@ -32450,17 +32640,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR179" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS179" t="inlineStr">
         <is>
           <t>SER_NO_FHI_107_MONTHLY</t>
         </is>
       </c>
       <c r="AT179" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU179" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV179" t="inlineStr">
@@ -32676,7 +32871,7 @@
       </c>
       <c r="AP180" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ180" t="inlineStr">
@@ -32684,17 +32879,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR180" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS180" t="inlineStr">
         <is>
           <t>SER_NO_FHI_107_MONTHLY</t>
         </is>
       </c>
       <c r="AT180" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU180" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV180" t="inlineStr">
@@ -33228,7 +33428,7 @@
       </c>
       <c r="AP183" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ183" t="inlineStr">
@@ -33236,17 +33436,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR183" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS183" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_MEASLES</t>
         </is>
       </c>
       <c r="AT183" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU183" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV183" t="inlineStr">
@@ -33462,7 +33667,7 @@
       </c>
       <c r="AP184" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ184" t="inlineStr">
@@ -33470,17 +33675,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR184" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS184" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_MEASLES</t>
         </is>
       </c>
       <c r="AT184" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU184" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV184" t="inlineStr">
@@ -36067,7 +36277,7 @@
       </c>
       <c r="AP199" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ199" t="inlineStr">
@@ -36075,17 +36285,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR199" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS199" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_170</t>
         </is>
       </c>
       <c r="AT199" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU199" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV199" t="inlineStr">
@@ -36301,7 +36516,7 @@
       </c>
       <c r="AP200" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ200" t="inlineStr">
@@ -36309,17 +36524,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR200" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS200" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_170</t>
         </is>
       </c>
       <c r="AT200" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU200" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV200" t="inlineStr">
@@ -36605,7 +36825,7 @@
       </c>
       <c r="AP202" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ202" t="inlineStr">
@@ -36613,17 +36833,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR202" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS202" t="inlineStr">
         <is>
           <t>SER_NO_FHI_107_MONTHLY</t>
         </is>
       </c>
       <c r="AT202" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU202" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV202" t="inlineStr">
@@ -36839,7 +37064,7 @@
       </c>
       <c r="AP203" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ203" t="inlineStr">
@@ -36847,17 +37072,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR203" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS203" t="inlineStr">
         <is>
           <t>SER_NO_FHI_107_MONTHLY</t>
         </is>
       </c>
       <c r="AT203" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU203" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV203" t="inlineStr">
